--- a/WBS/開発マイルストーン_WBS.xlsx
+++ b/WBS/開発マイルストーン_WBS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>開発マイルストーン WBS</t>
   </si>
@@ -28,10 +28,10 @@
     <t>プロジェクト名</t>
   </si>
   <si>
-    <t>基準日</t>
-  </si>
-  <si>
-    <t>ガント表示日数</t>
+    <t>開始月</t>
+  </si>
+  <si>
+    <t>終了月</t>
   </si>
   <si>
     <t>週末設定</t>
@@ -40,19 +40,28 @@
     <t>今日の日付</t>
   </si>
   <si>
+    <t>入力補助</t>
+  </si>
+  <si>
     <t>サンプル開発プロジェクト</t>
   </si>
   <si>
     <t>土日休み</t>
   </si>
   <si>
+    <t>WBSで入力ダイアログを実行</t>
+  </si>
+  <si>
     <t>操作</t>
   </si>
   <si>
-    <t>入力後、VBAの RefreshWBS を実行するとガント・終了日・遅れが再計算されます。</t>
+    <t>開始月・終了月を変更すると、ガントの日付範囲が連動します。</t>
   </si>
   <si>
     <t>VBAの AddWBSRow で入力行を追加できます。</t>
+  </si>
+  <si>
+    <t>VBAの InputWBSRow で選択行へ入力ダイアログを表示できます。</t>
   </si>
   <si>
     <t>休日シートに日付を追加すると、予定終了日から除外されます。</t>
@@ -245,11 +254,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="m/d"/>
-    <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0%"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="m月"/>
+    <numFmt numFmtId="165" formatCode="m/d"/>
+    <numFmt numFmtId="166" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="yyyy/m"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -400,26 +411,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -430,13 +444,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
@@ -785,7 +800,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EG105"/>
+  <dimension ref="A1:NS105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -799,10 +814,10 @@
     <col min="15" max="15" width="8.7109375" customWidth="1"/>
     <col min="16" max="16" width="24.7109375" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" customWidth="1"/>
-    <col min="18" max="137" width="3.85546875" customWidth="1"/>
+    <col min="18" max="383" width="3.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:137" ht="32" customHeight="1">
+    <row r="1" spans="1:383" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,9 +838,9 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:137">
+    <row r="2" spans="1:383">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -844,7 +859,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="4" spans="1:137" ht="22" customHeight="1">
+    <row r="4" spans="1:383" ht="22" customHeight="1">
       <c r="R4" s="3">
         <v>46296</v>
       </c>
@@ -1205,3110 +1220,4586 @@
       <c r="EG4" s="3">
         <v>46415</v>
       </c>
-    </row>
-    <row r="5" spans="1:137" ht="34" customHeight="1">
+      <c r="EH4" s="3">
+        <v>46416</v>
+      </c>
+      <c r="EI4" s="3">
+        <v>46417</v>
+      </c>
+      <c r="EJ4" s="3">
+        <v>46418</v>
+      </c>
+      <c r="EK4" s="3">
+        <v>46419</v>
+      </c>
+      <c r="EL4" s="3">
+        <v>46420</v>
+      </c>
+      <c r="EM4" s="3">
+        <v>46421</v>
+      </c>
+      <c r="EN4" s="3">
+        <v>46422</v>
+      </c>
+      <c r="EO4" s="3">
+        <v>46423</v>
+      </c>
+      <c r="EP4" s="3">
+        <v>46424</v>
+      </c>
+      <c r="EQ4" s="3">
+        <v>46425</v>
+      </c>
+      <c r="ER4" s="3">
+        <v>46426</v>
+      </c>
+      <c r="ES4" s="3">
+        <v>46427</v>
+      </c>
+      <c r="ET4" s="3">
+        <v>46428</v>
+      </c>
+      <c r="EU4" s="3">
+        <v>46429</v>
+      </c>
+      <c r="EV4" s="3">
+        <v>46430</v>
+      </c>
+      <c r="EW4" s="3">
+        <v>46431</v>
+      </c>
+      <c r="EX4" s="3">
+        <v>46432</v>
+      </c>
+      <c r="EY4" s="3">
+        <v>46433</v>
+      </c>
+      <c r="EZ4" s="3">
+        <v>46434</v>
+      </c>
+      <c r="FA4" s="3">
+        <v>46435</v>
+      </c>
+      <c r="FB4" s="3">
+        <v>46436</v>
+      </c>
+      <c r="FC4" s="3">
+        <v>46437</v>
+      </c>
+      <c r="FD4" s="3">
+        <v>46438</v>
+      </c>
+      <c r="FE4" s="3">
+        <v>46439</v>
+      </c>
+      <c r="FF4" s="3">
+        <v>46440</v>
+      </c>
+      <c r="FG4" s="3">
+        <v>46441</v>
+      </c>
+      <c r="FH4" s="3">
+        <v>46442</v>
+      </c>
+      <c r="FI4" s="3">
+        <v>46443</v>
+      </c>
+      <c r="FJ4" s="3">
+        <v>46444</v>
+      </c>
+      <c r="FK4" s="3">
+        <v>46445</v>
+      </c>
+      <c r="FL4" s="3">
+        <v>46446</v>
+      </c>
+      <c r="FM4" s="3">
+        <v>46447</v>
+      </c>
+      <c r="FN4" s="3">
+        <v>46448</v>
+      </c>
+      <c r="FO4" s="3">
+        <v>46449</v>
+      </c>
+      <c r="FP4" s="3">
+        <v>46450</v>
+      </c>
+      <c r="FQ4" s="3">
+        <v>46451</v>
+      </c>
+      <c r="FR4" s="3">
+        <v>46452</v>
+      </c>
+      <c r="FS4" s="3">
+        <v>46453</v>
+      </c>
+      <c r="FT4" s="3">
+        <v>46454</v>
+      </c>
+      <c r="FU4" s="3">
+        <v>46455</v>
+      </c>
+      <c r="FV4" s="3">
+        <v>46456</v>
+      </c>
+      <c r="FW4" s="3">
+        <v>46457</v>
+      </c>
+      <c r="FX4" s="3">
+        <v>46458</v>
+      </c>
+      <c r="FY4" s="3">
+        <v>46459</v>
+      </c>
+      <c r="FZ4" s="3">
+        <v>46460</v>
+      </c>
+      <c r="GA4" s="3">
+        <v>46461</v>
+      </c>
+      <c r="GB4" s="3">
+        <v>46462</v>
+      </c>
+      <c r="GC4" s="3">
+        <v>46463</v>
+      </c>
+      <c r="GD4" s="3">
+        <v>46464</v>
+      </c>
+      <c r="GE4" s="3">
+        <v>46465</v>
+      </c>
+      <c r="GF4" s="3">
+        <v>46466</v>
+      </c>
+      <c r="GG4" s="3">
+        <v>46467</v>
+      </c>
+      <c r="GH4" s="3">
+        <v>46468</v>
+      </c>
+      <c r="GI4" s="3">
+        <v>46469</v>
+      </c>
+      <c r="GJ4" s="3">
+        <v>46470</v>
+      </c>
+      <c r="GK4" s="3">
+        <v>46471</v>
+      </c>
+      <c r="GL4" s="3">
+        <v>46472</v>
+      </c>
+      <c r="GM4" s="3">
+        <v>46473</v>
+      </c>
+      <c r="GN4" s="3">
+        <v>46474</v>
+      </c>
+      <c r="GO4" s="3">
+        <v>46475</v>
+      </c>
+      <c r="GP4" s="3">
+        <v>46476</v>
+      </c>
+      <c r="GQ4" s="3">
+        <v>46477</v>
+      </c>
+      <c r="GR4" s="3">
+        <v>46478</v>
+      </c>
+      <c r="GS4" s="3">
+        <v>46479</v>
+      </c>
+      <c r="GT4" s="3">
+        <v>46480</v>
+      </c>
+      <c r="GU4" s="3">
+        <v>46481</v>
+      </c>
+      <c r="GV4" s="3">
+        <v>46482</v>
+      </c>
+      <c r="GW4" s="3">
+        <v>46483</v>
+      </c>
+      <c r="GX4" s="3">
+        <v>46484</v>
+      </c>
+      <c r="GY4" s="3">
+        <v>46485</v>
+      </c>
+      <c r="GZ4" s="3">
+        <v>46486</v>
+      </c>
+      <c r="HA4" s="3">
+        <v>46487</v>
+      </c>
+      <c r="HB4" s="3">
+        <v>46488</v>
+      </c>
+      <c r="HC4" s="3">
+        <v>46489</v>
+      </c>
+      <c r="HD4" s="3">
+        <v>46490</v>
+      </c>
+      <c r="HE4" s="3">
+        <v>46491</v>
+      </c>
+      <c r="HF4" s="3">
+        <v>46492</v>
+      </c>
+      <c r="HG4" s="3">
+        <v>46493</v>
+      </c>
+      <c r="HH4" s="3">
+        <v>46494</v>
+      </c>
+      <c r="HI4" s="3">
+        <v>46495</v>
+      </c>
+      <c r="HJ4" s="3">
+        <v>46496</v>
+      </c>
+      <c r="HK4" s="3">
+        <v>46497</v>
+      </c>
+      <c r="HL4" s="3">
+        <v>46498</v>
+      </c>
+      <c r="HM4" s="3">
+        <v>46499</v>
+      </c>
+      <c r="HN4" s="3">
+        <v>46500</v>
+      </c>
+      <c r="HO4" s="3">
+        <v>46501</v>
+      </c>
+      <c r="HP4" s="3">
+        <v>46502</v>
+      </c>
+      <c r="HQ4" s="3">
+        <v>46503</v>
+      </c>
+      <c r="HR4" s="3">
+        <v>46504</v>
+      </c>
+      <c r="HS4" s="3">
+        <v>46505</v>
+      </c>
+      <c r="HT4" s="3">
+        <v>46506</v>
+      </c>
+      <c r="HU4" s="3">
+        <v>46507</v>
+      </c>
+      <c r="HV4" s="3">
+        <v>46508</v>
+      </c>
+      <c r="HW4" s="3">
+        <v>46509</v>
+      </c>
+      <c r="HX4" s="3">
+        <v>46510</v>
+      </c>
+      <c r="HY4" s="3">
+        <v>46511</v>
+      </c>
+      <c r="HZ4" s="3">
+        <v>46512</v>
+      </c>
+      <c r="IA4" s="3">
+        <v>46513</v>
+      </c>
+      <c r="IB4" s="3">
+        <v>46514</v>
+      </c>
+      <c r="IC4" s="3">
+        <v>46515</v>
+      </c>
+      <c r="ID4" s="3">
+        <v>46516</v>
+      </c>
+      <c r="IE4" s="3">
+        <v>46517</v>
+      </c>
+      <c r="IF4" s="3">
+        <v>46518</v>
+      </c>
+      <c r="IG4" s="3">
+        <v>46519</v>
+      </c>
+      <c r="IH4" s="3">
+        <v>46520</v>
+      </c>
+      <c r="II4" s="3">
+        <v>46521</v>
+      </c>
+      <c r="IJ4" s="3">
+        <v>46522</v>
+      </c>
+      <c r="IK4" s="3">
+        <v>46523</v>
+      </c>
+      <c r="IL4" s="3">
+        <v>46524</v>
+      </c>
+      <c r="IM4" s="3">
+        <v>46525</v>
+      </c>
+      <c r="IN4" s="3">
+        <v>46526</v>
+      </c>
+      <c r="IO4" s="3">
+        <v>46527</v>
+      </c>
+      <c r="IP4" s="3">
+        <v>46528</v>
+      </c>
+      <c r="IQ4" s="3">
+        <v>46529</v>
+      </c>
+      <c r="IR4" s="3">
+        <v>46530</v>
+      </c>
+      <c r="IS4" s="3">
+        <v>46531</v>
+      </c>
+      <c r="IT4" s="3">
+        <v>46532</v>
+      </c>
+      <c r="IU4" s="3">
+        <v>46533</v>
+      </c>
+      <c r="IV4" s="3">
+        <v>46534</v>
+      </c>
+      <c r="IW4" s="3">
+        <v>46535</v>
+      </c>
+      <c r="IX4" s="3">
+        <v>46536</v>
+      </c>
+      <c r="IY4" s="3">
+        <v>46537</v>
+      </c>
+      <c r="IZ4" s="3">
+        <v>46538</v>
+      </c>
+      <c r="JA4" s="3">
+        <v>46539</v>
+      </c>
+      <c r="JB4" s="3">
+        <v>46540</v>
+      </c>
+      <c r="JC4" s="3">
+        <v>46541</v>
+      </c>
+      <c r="JD4" s="3">
+        <v>46542</v>
+      </c>
+      <c r="JE4" s="3">
+        <v>46543</v>
+      </c>
+      <c r="JF4" s="3">
+        <v>46544</v>
+      </c>
+      <c r="JG4" s="3">
+        <v>46545</v>
+      </c>
+      <c r="JH4" s="3">
+        <v>46546</v>
+      </c>
+      <c r="JI4" s="3">
+        <v>46547</v>
+      </c>
+      <c r="JJ4" s="3">
+        <v>46548</v>
+      </c>
+      <c r="JK4" s="3">
+        <v>46549</v>
+      </c>
+      <c r="JL4" s="3">
+        <v>46550</v>
+      </c>
+      <c r="JM4" s="3">
+        <v>46551</v>
+      </c>
+      <c r="JN4" s="3">
+        <v>46552</v>
+      </c>
+      <c r="JO4" s="3">
+        <v>46553</v>
+      </c>
+      <c r="JP4" s="3">
+        <v>46554</v>
+      </c>
+      <c r="JQ4" s="3">
+        <v>46555</v>
+      </c>
+      <c r="JR4" s="3">
+        <v>46556</v>
+      </c>
+      <c r="JS4" s="3">
+        <v>46557</v>
+      </c>
+      <c r="JT4" s="3">
+        <v>46558</v>
+      </c>
+      <c r="JU4" s="3">
+        <v>46559</v>
+      </c>
+      <c r="JV4" s="3">
+        <v>46560</v>
+      </c>
+      <c r="JW4" s="3">
+        <v>46561</v>
+      </c>
+      <c r="JX4" s="3">
+        <v>46562</v>
+      </c>
+      <c r="JY4" s="3">
+        <v>46563</v>
+      </c>
+      <c r="JZ4" s="3">
+        <v>46564</v>
+      </c>
+      <c r="KA4" s="3">
+        <v>46565</v>
+      </c>
+      <c r="KB4" s="3">
+        <v>46566</v>
+      </c>
+      <c r="KC4" s="3">
+        <v>46567</v>
+      </c>
+      <c r="KD4" s="3">
+        <v>46568</v>
+      </c>
+      <c r="KE4" s="3">
+        <v>46569</v>
+      </c>
+      <c r="KF4" s="3">
+        <v>46570</v>
+      </c>
+      <c r="KG4" s="3">
+        <v>46571</v>
+      </c>
+      <c r="KH4" s="3">
+        <v>46572</v>
+      </c>
+      <c r="KI4" s="3">
+        <v>46573</v>
+      </c>
+      <c r="KJ4" s="3">
+        <v>46574</v>
+      </c>
+      <c r="KK4" s="3">
+        <v>46575</v>
+      </c>
+      <c r="KL4" s="3">
+        <v>46576</v>
+      </c>
+      <c r="KM4" s="3">
+        <v>46577</v>
+      </c>
+      <c r="KN4" s="3">
+        <v>46578</v>
+      </c>
+      <c r="KO4" s="3">
+        <v>46579</v>
+      </c>
+      <c r="KP4" s="3">
+        <v>46580</v>
+      </c>
+      <c r="KQ4" s="3">
+        <v>46581</v>
+      </c>
+      <c r="KR4" s="3">
+        <v>46582</v>
+      </c>
+      <c r="KS4" s="3">
+        <v>46583</v>
+      </c>
+      <c r="KT4" s="3">
+        <v>46584</v>
+      </c>
+      <c r="KU4" s="3">
+        <v>46585</v>
+      </c>
+      <c r="KV4" s="3">
+        <v>46586</v>
+      </c>
+      <c r="KW4" s="3">
+        <v>46587</v>
+      </c>
+      <c r="KX4" s="3">
+        <v>46588</v>
+      </c>
+      <c r="KY4" s="3">
+        <v>46589</v>
+      </c>
+      <c r="KZ4" s="3">
+        <v>46590</v>
+      </c>
+      <c r="LA4" s="3">
+        <v>46591</v>
+      </c>
+      <c r="LB4" s="3">
+        <v>46592</v>
+      </c>
+      <c r="LC4" s="3">
+        <v>46593</v>
+      </c>
+      <c r="LD4" s="3">
+        <v>46594</v>
+      </c>
+      <c r="LE4" s="3">
+        <v>46595</v>
+      </c>
+      <c r="LF4" s="3">
+        <v>46596</v>
+      </c>
+      <c r="LG4" s="3">
+        <v>46597</v>
+      </c>
+      <c r="LH4" s="3">
+        <v>46598</v>
+      </c>
+      <c r="LI4" s="3">
+        <v>46599</v>
+      </c>
+      <c r="LJ4" s="3">
+        <v>46600</v>
+      </c>
+      <c r="LK4" s="3">
+        <v>46601</v>
+      </c>
+      <c r="LL4" s="3">
+        <v>46602</v>
+      </c>
+      <c r="LM4" s="3">
+        <v>46603</v>
+      </c>
+      <c r="LN4" s="3">
+        <v>46604</v>
+      </c>
+      <c r="LO4" s="3">
+        <v>46605</v>
+      </c>
+      <c r="LP4" s="3">
+        <v>46606</v>
+      </c>
+      <c r="LQ4" s="3">
+        <v>46607</v>
+      </c>
+      <c r="LR4" s="3">
+        <v>46608</v>
+      </c>
+      <c r="LS4" s="3">
+        <v>46609</v>
+      </c>
+      <c r="LT4" s="3">
+        <v>46610</v>
+      </c>
+      <c r="LU4" s="3">
+        <v>46611</v>
+      </c>
+      <c r="LV4" s="3">
+        <v>46612</v>
+      </c>
+      <c r="LW4" s="3">
+        <v>46613</v>
+      </c>
+      <c r="LX4" s="3">
+        <v>46614</v>
+      </c>
+      <c r="LY4" s="3">
+        <v>46615</v>
+      </c>
+      <c r="LZ4" s="3">
+        <v>46616</v>
+      </c>
+      <c r="MA4" s="3">
+        <v>46617</v>
+      </c>
+      <c r="MB4" s="3">
+        <v>46618</v>
+      </c>
+      <c r="MC4" s="3">
+        <v>46619</v>
+      </c>
+      <c r="MD4" s="3">
+        <v>46620</v>
+      </c>
+      <c r="ME4" s="3">
+        <v>46621</v>
+      </c>
+      <c r="MF4" s="3">
+        <v>46622</v>
+      </c>
+      <c r="MG4" s="3">
+        <v>46623</v>
+      </c>
+      <c r="MH4" s="3">
+        <v>46624</v>
+      </c>
+      <c r="MI4" s="3">
+        <v>46625</v>
+      </c>
+      <c r="MJ4" s="3">
+        <v>46626</v>
+      </c>
+      <c r="MK4" s="3">
+        <v>46627</v>
+      </c>
+      <c r="ML4" s="3">
+        <v>46628</v>
+      </c>
+      <c r="MM4" s="3">
+        <v>46629</v>
+      </c>
+      <c r="MN4" s="3">
+        <v>46630</v>
+      </c>
+      <c r="MO4" s="3">
+        <v>46631</v>
+      </c>
+      <c r="MP4" s="3">
+        <v>46632</v>
+      </c>
+      <c r="MQ4" s="3">
+        <v>46633</v>
+      </c>
+      <c r="MR4" s="3">
+        <v>46634</v>
+      </c>
+      <c r="MS4" s="3">
+        <v>46635</v>
+      </c>
+      <c r="MT4" s="3">
+        <v>46636</v>
+      </c>
+      <c r="MU4" s="3">
+        <v>46637</v>
+      </c>
+      <c r="MV4" s="3">
+        <v>46638</v>
+      </c>
+      <c r="MW4" s="3">
+        <v>46639</v>
+      </c>
+      <c r="MX4" s="3">
+        <v>46640</v>
+      </c>
+      <c r="MY4" s="3">
+        <v>46641</v>
+      </c>
+      <c r="MZ4" s="3">
+        <v>46642</v>
+      </c>
+      <c r="NA4" s="3">
+        <v>46643</v>
+      </c>
+      <c r="NB4" s="3">
+        <v>46644</v>
+      </c>
+      <c r="NC4" s="3">
+        <v>46645</v>
+      </c>
+      <c r="ND4" s="3">
+        <v>46646</v>
+      </c>
+      <c r="NE4" s="3">
+        <v>46647</v>
+      </c>
+      <c r="NF4" s="3">
+        <v>46648</v>
+      </c>
+      <c r="NG4" s="3">
+        <v>46649</v>
+      </c>
+      <c r="NH4" s="3">
+        <v>46650</v>
+      </c>
+      <c r="NI4" s="3">
+        <v>46651</v>
+      </c>
+      <c r="NJ4" s="3">
+        <v>46652</v>
+      </c>
+      <c r="NK4" s="3">
+        <v>46653</v>
+      </c>
+      <c r="NL4" s="3">
+        <v>46654</v>
+      </c>
+      <c r="NM4" s="3">
+        <v>46655</v>
+      </c>
+      <c r="NN4" s="3">
+        <v>46656</v>
+      </c>
+      <c r="NO4" s="3">
+        <v>46657</v>
+      </c>
+      <c r="NP4" s="3">
+        <v>46658</v>
+      </c>
+      <c r="NQ4" s="3">
+        <v>46659</v>
+      </c>
+      <c r="NR4" s="3">
+        <v>46660</v>
+      </c>
+      <c r="NS4" s="3">
+        <v>46661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:383" ht="34" customHeight="1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="4">
+        <v>46296</v>
+      </c>
+      <c r="S5" s="4">
+        <v>46297</v>
+      </c>
+      <c r="T5" s="4">
+        <v>46298</v>
+      </c>
+      <c r="U5" s="4">
+        <v>46299</v>
+      </c>
+      <c r="V5" s="4">
+        <v>46300</v>
+      </c>
+      <c r="W5" s="4">
+        <v>46301</v>
+      </c>
+      <c r="X5" s="4">
+        <v>46302</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>46303</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>46304</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>46305</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>46306</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>46307</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>46308</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>46309</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>46310</v>
+      </c>
+      <c r="AG5" s="4">
+        <v>46311</v>
+      </c>
+      <c r="AH5" s="4">
+        <v>46312</v>
+      </c>
+      <c r="AI5" s="4">
+        <v>46313</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>46314</v>
+      </c>
+      <c r="AK5" s="4">
+        <v>46315</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>46316</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>46317</v>
+      </c>
+      <c r="AN5" s="4">
+        <v>46318</v>
+      </c>
+      <c r="AO5" s="4">
+        <v>46319</v>
+      </c>
+      <c r="AP5" s="4">
+        <v>46320</v>
+      </c>
+      <c r="AQ5" s="4">
+        <v>46321</v>
+      </c>
+      <c r="AR5" s="4">
+        <v>46322</v>
+      </c>
+      <c r="AS5" s="4">
+        <v>46323</v>
+      </c>
+      <c r="AT5" s="4">
+        <v>46324</v>
+      </c>
+      <c r="AU5" s="4">
+        <v>46325</v>
+      </c>
+      <c r="AV5" s="4">
+        <v>46326</v>
+      </c>
+      <c r="AW5" s="4">
+        <v>46327</v>
+      </c>
+      <c r="AX5" s="4">
+        <v>46328</v>
+      </c>
+      <c r="AY5" s="4">
+        <v>46329</v>
+      </c>
+      <c r="AZ5" s="4">
+        <v>46330</v>
+      </c>
+      <c r="BA5" s="4">
+        <v>46331</v>
+      </c>
+      <c r="BB5" s="4">
+        <v>46332</v>
+      </c>
+      <c r="BC5" s="4">
+        <v>46333</v>
+      </c>
+      <c r="BD5" s="4">
+        <v>46334</v>
+      </c>
+      <c r="BE5" s="4">
+        <v>46335</v>
+      </c>
+      <c r="BF5" s="4">
+        <v>46336</v>
+      </c>
+      <c r="BG5" s="4">
+        <v>46337</v>
+      </c>
+      <c r="BH5" s="4">
+        <v>46338</v>
+      </c>
+      <c r="BI5" s="4">
+        <v>46339</v>
+      </c>
+      <c r="BJ5" s="4">
+        <v>46340</v>
+      </c>
+      <c r="BK5" s="4">
+        <v>46341</v>
+      </c>
+      <c r="BL5" s="4">
+        <v>46342</v>
+      </c>
+      <c r="BM5" s="4">
+        <v>46343</v>
+      </c>
+      <c r="BN5" s="4">
+        <v>46344</v>
+      </c>
+      <c r="BO5" s="4">
+        <v>46345</v>
+      </c>
+      <c r="BP5" s="4">
+        <v>46346</v>
+      </c>
+      <c r="BQ5" s="4">
+        <v>46347</v>
+      </c>
+      <c r="BR5" s="4">
+        <v>46348</v>
+      </c>
+      <c r="BS5" s="4">
+        <v>46349</v>
+      </c>
+      <c r="BT5" s="4">
+        <v>46350</v>
+      </c>
+      <c r="BU5" s="4">
+        <v>46351</v>
+      </c>
+      <c r="BV5" s="4">
+        <v>46352</v>
+      </c>
+      <c r="BW5" s="4">
+        <v>46353</v>
+      </c>
+      <c r="BX5" s="4">
+        <v>46354</v>
+      </c>
+      <c r="BY5" s="4">
+        <v>46355</v>
+      </c>
+      <c r="BZ5" s="4">
+        <v>46356</v>
+      </c>
+      <c r="CA5" s="4">
+        <v>46357</v>
+      </c>
+      <c r="CB5" s="4">
+        <v>46358</v>
+      </c>
+      <c r="CC5" s="4">
+        <v>46359</v>
+      </c>
+      <c r="CD5" s="4">
+        <v>46360</v>
+      </c>
+      <c r="CE5" s="4">
+        <v>46361</v>
+      </c>
+      <c r="CF5" s="4">
+        <v>46362</v>
+      </c>
+      <c r="CG5" s="4">
+        <v>46363</v>
+      </c>
+      <c r="CH5" s="4">
+        <v>46364</v>
+      </c>
+      <c r="CI5" s="4">
+        <v>46365</v>
+      </c>
+      <c r="CJ5" s="4">
+        <v>46366</v>
+      </c>
+      <c r="CK5" s="4">
+        <v>46367</v>
+      </c>
+      <c r="CL5" s="4">
+        <v>46368</v>
+      </c>
+      <c r="CM5" s="4">
+        <v>46369</v>
+      </c>
+      <c r="CN5" s="4">
+        <v>46370</v>
+      </c>
+      <c r="CO5" s="4">
+        <v>46371</v>
+      </c>
+      <c r="CP5" s="4">
+        <v>46372</v>
+      </c>
+      <c r="CQ5" s="4">
+        <v>46373</v>
+      </c>
+      <c r="CR5" s="4">
+        <v>46374</v>
+      </c>
+      <c r="CS5" s="4">
+        <v>46375</v>
+      </c>
+      <c r="CT5" s="4">
+        <v>46376</v>
+      </c>
+      <c r="CU5" s="4">
+        <v>46377</v>
+      </c>
+      <c r="CV5" s="4">
+        <v>46378</v>
+      </c>
+      <c r="CW5" s="4">
+        <v>46379</v>
+      </c>
+      <c r="CX5" s="4">
+        <v>46380</v>
+      </c>
+      <c r="CY5" s="4">
+        <v>46381</v>
+      </c>
+      <c r="CZ5" s="4">
+        <v>46382</v>
+      </c>
+      <c r="DA5" s="4">
+        <v>46383</v>
+      </c>
+      <c r="DB5" s="4">
+        <v>46384</v>
+      </c>
+      <c r="DC5" s="4">
+        <v>46385</v>
+      </c>
+      <c r="DD5" s="4">
+        <v>46386</v>
+      </c>
+      <c r="DE5" s="4">
+        <v>46387</v>
+      </c>
+      <c r="DF5" s="4">
+        <v>46388</v>
+      </c>
+      <c r="DG5" s="4">
+        <v>46389</v>
+      </c>
+      <c r="DH5" s="4">
+        <v>46390</v>
+      </c>
+      <c r="DI5" s="4">
+        <v>46391</v>
+      </c>
+      <c r="DJ5" s="4">
+        <v>46392</v>
+      </c>
+      <c r="DK5" s="4">
+        <v>46393</v>
+      </c>
+      <c r="DL5" s="4">
+        <v>46394</v>
+      </c>
+      <c r="DM5" s="4">
+        <v>46395</v>
+      </c>
+      <c r="DN5" s="4">
+        <v>46396</v>
+      </c>
+      <c r="DO5" s="4">
+        <v>46397</v>
+      </c>
+      <c r="DP5" s="4">
+        <v>46398</v>
+      </c>
+      <c r="DQ5" s="4">
+        <v>46399</v>
+      </c>
+      <c r="DR5" s="4">
+        <v>46400</v>
+      </c>
+      <c r="DS5" s="4">
+        <v>46401</v>
+      </c>
+      <c r="DT5" s="4">
+        <v>46402</v>
+      </c>
+      <c r="DU5" s="4">
+        <v>46403</v>
+      </c>
+      <c r="DV5" s="4">
+        <v>46404</v>
+      </c>
+      <c r="DW5" s="4">
+        <v>46405</v>
+      </c>
+      <c r="DX5" s="4">
+        <v>46406</v>
+      </c>
+      <c r="DY5" s="4">
+        <v>46407</v>
+      </c>
+      <c r="DZ5" s="4">
+        <v>46408</v>
+      </c>
+      <c r="EA5" s="4">
+        <v>46409</v>
+      </c>
+      <c r="EB5" s="4">
+        <v>46410</v>
+      </c>
+      <c r="EC5" s="4">
+        <v>46411</v>
+      </c>
+      <c r="ED5" s="4">
+        <v>46412</v>
+      </c>
+      <c r="EE5" s="4">
+        <v>46413</v>
+      </c>
+      <c r="EF5" s="4">
+        <v>46414</v>
+      </c>
+      <c r="EG5" s="4">
+        <v>46415</v>
+      </c>
+      <c r="EH5" s="4">
+        <v>46416</v>
+      </c>
+      <c r="EI5" s="4">
+        <v>46417</v>
+      </c>
+      <c r="EJ5" s="4">
+        <v>46418</v>
+      </c>
+      <c r="EK5" s="4">
+        <v>46419</v>
+      </c>
+      <c r="EL5" s="4">
+        <v>46420</v>
+      </c>
+      <c r="EM5" s="4">
+        <v>46421</v>
+      </c>
+      <c r="EN5" s="4">
+        <v>46422</v>
+      </c>
+      <c r="EO5" s="4">
+        <v>46423</v>
+      </c>
+      <c r="EP5" s="4">
+        <v>46424</v>
+      </c>
+      <c r="EQ5" s="4">
+        <v>46425</v>
+      </c>
+      <c r="ER5" s="4">
+        <v>46426</v>
+      </c>
+      <c r="ES5" s="4">
+        <v>46427</v>
+      </c>
+      <c r="ET5" s="4">
+        <v>46428</v>
+      </c>
+      <c r="EU5" s="4">
+        <v>46429</v>
+      </c>
+      <c r="EV5" s="4">
+        <v>46430</v>
+      </c>
+      <c r="EW5" s="4">
+        <v>46431</v>
+      </c>
+      <c r="EX5" s="4">
+        <v>46432</v>
+      </c>
+      <c r="EY5" s="4">
+        <v>46433</v>
+      </c>
+      <c r="EZ5" s="4">
+        <v>46434</v>
+      </c>
+      <c r="FA5" s="4">
+        <v>46435</v>
+      </c>
+      <c r="FB5" s="4">
+        <v>46436</v>
+      </c>
+      <c r="FC5" s="4">
+        <v>46437</v>
+      </c>
+      <c r="FD5" s="4">
+        <v>46438</v>
+      </c>
+      <c r="FE5" s="4">
+        <v>46439</v>
+      </c>
+      <c r="FF5" s="4">
+        <v>46440</v>
+      </c>
+      <c r="FG5" s="4">
+        <v>46441</v>
+      </c>
+      <c r="FH5" s="4">
+        <v>46442</v>
+      </c>
+      <c r="FI5" s="4">
+        <v>46443</v>
+      </c>
+      <c r="FJ5" s="4">
+        <v>46444</v>
+      </c>
+      <c r="FK5" s="4">
+        <v>46445</v>
+      </c>
+      <c r="FL5" s="4">
+        <v>46446</v>
+      </c>
+      <c r="FM5" s="4">
+        <v>46447</v>
+      </c>
+      <c r="FN5" s="4">
+        <v>46448</v>
+      </c>
+      <c r="FO5" s="4">
+        <v>46449</v>
+      </c>
+      <c r="FP5" s="4">
+        <v>46450</v>
+      </c>
+      <c r="FQ5" s="4">
+        <v>46451</v>
+      </c>
+      <c r="FR5" s="4">
+        <v>46452</v>
+      </c>
+      <c r="FS5" s="4">
+        <v>46453</v>
+      </c>
+      <c r="FT5" s="4">
+        <v>46454</v>
+      </c>
+      <c r="FU5" s="4">
+        <v>46455</v>
+      </c>
+      <c r="FV5" s="4">
+        <v>46456</v>
+      </c>
+      <c r="FW5" s="4">
+        <v>46457</v>
+      </c>
+      <c r="FX5" s="4">
+        <v>46458</v>
+      </c>
+      <c r="FY5" s="4">
+        <v>46459</v>
+      </c>
+      <c r="FZ5" s="4">
+        <v>46460</v>
+      </c>
+      <c r="GA5" s="4">
+        <v>46461</v>
+      </c>
+      <c r="GB5" s="4">
+        <v>46462</v>
+      </c>
+      <c r="GC5" s="4">
+        <v>46463</v>
+      </c>
+      <c r="GD5" s="4">
+        <v>46464</v>
+      </c>
+      <c r="GE5" s="4">
+        <v>46465</v>
+      </c>
+      <c r="GF5" s="4">
+        <v>46466</v>
+      </c>
+      <c r="GG5" s="4">
+        <v>46467</v>
+      </c>
+      <c r="GH5" s="4">
+        <v>46468</v>
+      </c>
+      <c r="GI5" s="4">
+        <v>46469</v>
+      </c>
+      <c r="GJ5" s="4">
+        <v>46470</v>
+      </c>
+      <c r="GK5" s="4">
+        <v>46471</v>
+      </c>
+      <c r="GL5" s="4">
+        <v>46472</v>
+      </c>
+      <c r="GM5" s="4">
+        <v>46473</v>
+      </c>
+      <c r="GN5" s="4">
+        <v>46474</v>
+      </c>
+      <c r="GO5" s="4">
+        <v>46475</v>
+      </c>
+      <c r="GP5" s="4">
+        <v>46476</v>
+      </c>
+      <c r="GQ5" s="4">
+        <v>46477</v>
+      </c>
+      <c r="GR5" s="4">
+        <v>46478</v>
+      </c>
+      <c r="GS5" s="4">
+        <v>46479</v>
+      </c>
+      <c r="GT5" s="4">
+        <v>46480</v>
+      </c>
+      <c r="GU5" s="4">
+        <v>46481</v>
+      </c>
+      <c r="GV5" s="4">
+        <v>46482</v>
+      </c>
+      <c r="GW5" s="4">
+        <v>46483</v>
+      </c>
+      <c r="GX5" s="4">
+        <v>46484</v>
+      </c>
+      <c r="GY5" s="4">
+        <v>46485</v>
+      </c>
+      <c r="GZ5" s="4">
+        <v>46486</v>
+      </c>
+      <c r="HA5" s="4">
+        <v>46487</v>
+      </c>
+      <c r="HB5" s="4">
+        <v>46488</v>
+      </c>
+      <c r="HC5" s="4">
+        <v>46489</v>
+      </c>
+      <c r="HD5" s="4">
+        <v>46490</v>
+      </c>
+      <c r="HE5" s="4">
+        <v>46491</v>
+      </c>
+      <c r="HF5" s="4">
+        <v>46492</v>
+      </c>
+      <c r="HG5" s="4">
+        <v>46493</v>
+      </c>
+      <c r="HH5" s="4">
+        <v>46494</v>
+      </c>
+      <c r="HI5" s="4">
+        <v>46495</v>
+      </c>
+      <c r="HJ5" s="4">
+        <v>46496</v>
+      </c>
+      <c r="HK5" s="4">
+        <v>46497</v>
+      </c>
+      <c r="HL5" s="4">
+        <v>46498</v>
+      </c>
+      <c r="HM5" s="4">
+        <v>46499</v>
+      </c>
+      <c r="HN5" s="4">
+        <v>46500</v>
+      </c>
+      <c r="HO5" s="4">
+        <v>46501</v>
+      </c>
+      <c r="HP5" s="4">
+        <v>46502</v>
+      </c>
+      <c r="HQ5" s="4">
+        <v>46503</v>
+      </c>
+      <c r="HR5" s="4">
+        <v>46504</v>
+      </c>
+      <c r="HS5" s="4">
+        <v>46505</v>
+      </c>
+      <c r="HT5" s="4">
+        <v>46506</v>
+      </c>
+      <c r="HU5" s="4">
+        <v>46507</v>
+      </c>
+      <c r="HV5" s="4">
+        <v>46508</v>
+      </c>
+      <c r="HW5" s="4">
+        <v>46509</v>
+      </c>
+      <c r="HX5" s="4">
+        <v>46510</v>
+      </c>
+      <c r="HY5" s="4">
+        <v>46511</v>
+      </c>
+      <c r="HZ5" s="4">
+        <v>46512</v>
+      </c>
+      <c r="IA5" s="4">
+        <v>46513</v>
+      </c>
+      <c r="IB5" s="4">
+        <v>46514</v>
+      </c>
+      <c r="IC5" s="4">
+        <v>46515</v>
+      </c>
+      <c r="ID5" s="4">
+        <v>46516</v>
+      </c>
+      <c r="IE5" s="4">
+        <v>46517</v>
+      </c>
+      <c r="IF5" s="4">
+        <v>46518</v>
+      </c>
+      <c r="IG5" s="4">
+        <v>46519</v>
+      </c>
+      <c r="IH5" s="4">
+        <v>46520</v>
+      </c>
+      <c r="II5" s="4">
+        <v>46521</v>
+      </c>
+      <c r="IJ5" s="4">
+        <v>46522</v>
+      </c>
+      <c r="IK5" s="4">
+        <v>46523</v>
+      </c>
+      <c r="IL5" s="4">
+        <v>46524</v>
+      </c>
+      <c r="IM5" s="4">
+        <v>46525</v>
+      </c>
+      <c r="IN5" s="4">
+        <v>46526</v>
+      </c>
+      <c r="IO5" s="4">
+        <v>46527</v>
+      </c>
+      <c r="IP5" s="4">
+        <v>46528</v>
+      </c>
+      <c r="IQ5" s="4">
+        <v>46529</v>
+      </c>
+      <c r="IR5" s="4">
+        <v>46530</v>
+      </c>
+      <c r="IS5" s="4">
+        <v>46531</v>
+      </c>
+      <c r="IT5" s="4">
+        <v>46532</v>
+      </c>
+      <c r="IU5" s="4">
+        <v>46533</v>
+      </c>
+      <c r="IV5" s="4">
+        <v>46534</v>
+      </c>
+      <c r="IW5" s="4">
+        <v>46535</v>
+      </c>
+      <c r="IX5" s="4">
+        <v>46536</v>
+      </c>
+      <c r="IY5" s="4">
+        <v>46537</v>
+      </c>
+      <c r="IZ5" s="4">
+        <v>46538</v>
+      </c>
+      <c r="JA5" s="4">
+        <v>46539</v>
+      </c>
+      <c r="JB5" s="4">
+        <v>46540</v>
+      </c>
+      <c r="JC5" s="4">
+        <v>46541</v>
+      </c>
+      <c r="JD5" s="4">
+        <v>46542</v>
+      </c>
+      <c r="JE5" s="4">
+        <v>46543</v>
+      </c>
+      <c r="JF5" s="4">
+        <v>46544</v>
+      </c>
+      <c r="JG5" s="4">
+        <v>46545</v>
+      </c>
+      <c r="JH5" s="4">
+        <v>46546</v>
+      </c>
+      <c r="JI5" s="4">
+        <v>46547</v>
+      </c>
+      <c r="JJ5" s="4">
+        <v>46548</v>
+      </c>
+      <c r="JK5" s="4">
+        <v>46549</v>
+      </c>
+      <c r="JL5" s="4">
+        <v>46550</v>
+      </c>
+      <c r="JM5" s="4">
+        <v>46551</v>
+      </c>
+      <c r="JN5" s="4">
+        <v>46552</v>
+      </c>
+      <c r="JO5" s="4">
+        <v>46553</v>
+      </c>
+      <c r="JP5" s="4">
+        <v>46554</v>
+      </c>
+      <c r="JQ5" s="4">
+        <v>46555</v>
+      </c>
+      <c r="JR5" s="4">
+        <v>46556</v>
+      </c>
+      <c r="JS5" s="4">
+        <v>46557</v>
+      </c>
+      <c r="JT5" s="4">
+        <v>46558</v>
+      </c>
+      <c r="JU5" s="4">
+        <v>46559</v>
+      </c>
+      <c r="JV5" s="4">
+        <v>46560</v>
+      </c>
+      <c r="JW5" s="4">
+        <v>46561</v>
+      </c>
+      <c r="JX5" s="4">
+        <v>46562</v>
+      </c>
+      <c r="JY5" s="4">
+        <v>46563</v>
+      </c>
+      <c r="JZ5" s="4">
+        <v>46564</v>
+      </c>
+      <c r="KA5" s="4">
+        <v>46565</v>
+      </c>
+      <c r="KB5" s="4">
+        <v>46566</v>
+      </c>
+      <c r="KC5" s="4">
+        <v>46567</v>
+      </c>
+      <c r="KD5" s="4">
+        <v>46568</v>
+      </c>
+      <c r="KE5" s="4">
+        <v>46569</v>
+      </c>
+      <c r="KF5" s="4">
+        <v>46570</v>
+      </c>
+      <c r="KG5" s="4">
+        <v>46571</v>
+      </c>
+      <c r="KH5" s="4">
+        <v>46572</v>
+      </c>
+      <c r="KI5" s="4">
+        <v>46573</v>
+      </c>
+      <c r="KJ5" s="4">
+        <v>46574</v>
+      </c>
+      <c r="KK5" s="4">
+        <v>46575</v>
+      </c>
+      <c r="KL5" s="4">
+        <v>46576</v>
+      </c>
+      <c r="KM5" s="4">
+        <v>46577</v>
+      </c>
+      <c r="KN5" s="4">
+        <v>46578</v>
+      </c>
+      <c r="KO5" s="4">
+        <v>46579</v>
+      </c>
+      <c r="KP5" s="4">
+        <v>46580</v>
+      </c>
+      <c r="KQ5" s="4">
+        <v>46581</v>
+      </c>
+      <c r="KR5" s="4">
+        <v>46582</v>
+      </c>
+      <c r="KS5" s="4">
+        <v>46583</v>
+      </c>
+      <c r="KT5" s="4">
+        <v>46584</v>
+      </c>
+      <c r="KU5" s="4">
+        <v>46585</v>
+      </c>
+      <c r="KV5" s="4">
+        <v>46586</v>
+      </c>
+      <c r="KW5" s="4">
+        <v>46587</v>
+      </c>
+      <c r="KX5" s="4">
+        <v>46588</v>
+      </c>
+      <c r="KY5" s="4">
+        <v>46589</v>
+      </c>
+      <c r="KZ5" s="4">
+        <v>46590</v>
+      </c>
+      <c r="LA5" s="4">
+        <v>46591</v>
+      </c>
+      <c r="LB5" s="4">
+        <v>46592</v>
+      </c>
+      <c r="LC5" s="4">
+        <v>46593</v>
+      </c>
+      <c r="LD5" s="4">
+        <v>46594</v>
+      </c>
+      <c r="LE5" s="4">
+        <v>46595</v>
+      </c>
+      <c r="LF5" s="4">
+        <v>46596</v>
+      </c>
+      <c r="LG5" s="4">
+        <v>46597</v>
+      </c>
+      <c r="LH5" s="4">
+        <v>46598</v>
+      </c>
+      <c r="LI5" s="4">
+        <v>46599</v>
+      </c>
+      <c r="LJ5" s="4">
+        <v>46600</v>
+      </c>
+      <c r="LK5" s="4">
+        <v>46601</v>
+      </c>
+      <c r="LL5" s="4">
+        <v>46602</v>
+      </c>
+      <c r="LM5" s="4">
+        <v>46603</v>
+      </c>
+      <c r="LN5" s="4">
+        <v>46604</v>
+      </c>
+      <c r="LO5" s="4">
+        <v>46605</v>
+      </c>
+      <c r="LP5" s="4">
+        <v>46606</v>
+      </c>
+      <c r="LQ5" s="4">
+        <v>46607</v>
+      </c>
+      <c r="LR5" s="4">
+        <v>46608</v>
+      </c>
+      <c r="LS5" s="4">
+        <v>46609</v>
+      </c>
+      <c r="LT5" s="4">
+        <v>46610</v>
+      </c>
+      <c r="LU5" s="4">
+        <v>46611</v>
+      </c>
+      <c r="LV5" s="4">
+        <v>46612</v>
+      </c>
+      <c r="LW5" s="4">
+        <v>46613</v>
+      </c>
+      <c r="LX5" s="4">
+        <v>46614</v>
+      </c>
+      <c r="LY5" s="4">
+        <v>46615</v>
+      </c>
+      <c r="LZ5" s="4">
+        <v>46616</v>
+      </c>
+      <c r="MA5" s="4">
+        <v>46617</v>
+      </c>
+      <c r="MB5" s="4">
+        <v>46618</v>
+      </c>
+      <c r="MC5" s="4">
+        <v>46619</v>
+      </c>
+      <c r="MD5" s="4">
+        <v>46620</v>
+      </c>
+      <c r="ME5" s="4">
+        <v>46621</v>
+      </c>
+      <c r="MF5" s="4">
+        <v>46622</v>
+      </c>
+      <c r="MG5" s="4">
+        <v>46623</v>
+      </c>
+      <c r="MH5" s="4">
+        <v>46624</v>
+      </c>
+      <c r="MI5" s="4">
+        <v>46625</v>
+      </c>
+      <c r="MJ5" s="4">
+        <v>46626</v>
+      </c>
+      <c r="MK5" s="4">
+        <v>46627</v>
+      </c>
+      <c r="ML5" s="4">
+        <v>46628</v>
+      </c>
+      <c r="MM5" s="4">
+        <v>46629</v>
+      </c>
+      <c r="MN5" s="4">
+        <v>46630</v>
+      </c>
+      <c r="MO5" s="4">
+        <v>46631</v>
+      </c>
+      <c r="MP5" s="4">
+        <v>46632</v>
+      </c>
+      <c r="MQ5" s="4">
+        <v>46633</v>
+      </c>
+      <c r="MR5" s="4">
+        <v>46634</v>
+      </c>
+      <c r="MS5" s="4">
+        <v>46635</v>
+      </c>
+      <c r="MT5" s="4">
+        <v>46636</v>
+      </c>
+      <c r="MU5" s="4">
+        <v>46637</v>
+      </c>
+      <c r="MV5" s="4">
+        <v>46638</v>
+      </c>
+      <c r="MW5" s="4">
+        <v>46639</v>
+      </c>
+      <c r="MX5" s="4">
+        <v>46640</v>
+      </c>
+      <c r="MY5" s="4">
+        <v>46641</v>
+      </c>
+      <c r="MZ5" s="4">
+        <v>46642</v>
+      </c>
+      <c r="NA5" s="4">
+        <v>46643</v>
+      </c>
+      <c r="NB5" s="4">
+        <v>46644</v>
+      </c>
+      <c r="NC5" s="4">
+        <v>46645</v>
+      </c>
+      <c r="ND5" s="4">
+        <v>46646</v>
+      </c>
+      <c r="NE5" s="4">
+        <v>46647</v>
+      </c>
+      <c r="NF5" s="4">
+        <v>46648</v>
+      </c>
+      <c r="NG5" s="4">
+        <v>46649</v>
+      </c>
+      <c r="NH5" s="4">
+        <v>46650</v>
+      </c>
+      <c r="NI5" s="4">
+        <v>46651</v>
+      </c>
+      <c r="NJ5" s="4">
+        <v>46652</v>
+      </c>
+      <c r="NK5" s="4">
+        <v>46653</v>
+      </c>
+      <c r="NL5" s="4">
+        <v>46654</v>
+      </c>
+      <c r="NM5" s="4">
+        <v>46655</v>
+      </c>
+      <c r="NN5" s="4">
+        <v>46656</v>
+      </c>
+      <c r="NO5" s="4">
+        <v>46657</v>
+      </c>
+      <c r="NP5" s="4">
+        <v>46658</v>
+      </c>
+      <c r="NQ5" s="4">
+        <v>46659</v>
+      </c>
+      <c r="NR5" s="4">
+        <v>46660</v>
+      </c>
+      <c r="NS5" s="4">
+        <v>46661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:383">
+      <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46296</v>
+      </c>
+      <c r="G6" s="7">
+        <v>10</v>
+      </c>
+      <c r="H6" s="8">
+        <f>IF(OR(F6="",G6=""),"",WORKDAY.INTL(F6,G6-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="11">
+        <f>IF(OR(F6="",I6=""),"",NETWORKDAYS.INTL(F6,I6-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="11">
+        <f>IF(OR(H6="",J6=""),"",NETWORKDAYS.INTL(H6,J6-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>1</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="11">
+        <f>IF(C6="","",IF(E6="マイルストーン","MILESTONE",IF(K6&gt;=1,"完了",IF(I6&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:383">
+      <c r="A7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46296</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <f>IF(OR(F7="",G7=""),"",WORKDAY.INTL(F7,G7-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11">
+        <f>IF(OR(F7="",I7=""),"",NETWORKDAYS.INTL(F7,I7-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <f>IF(OR(H7="",J7=""),"",NETWORKDAYS.INTL(H7,J7-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="11">
+        <f>IF(C7="","",IF(E7="マイルストーン","MILESTONE",IF(K7&gt;=1,"完了",IF(I7&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:383">
+      <c r="A8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="10">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46297</v>
+      </c>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+      <c r="H8" s="8">
+        <f>IF(OR(F8="",G8=""),"",WORKDAY.INTL(F8,G8-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="11">
+        <f>IF(OR(F8="",I8=""),"",NETWORKDAYS.INTL(F8,I8-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <f>IF(OR(H8="",J8=""),"",NETWORKDAYS.INTL(H8,J8-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>1</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="11">
+        <f>IF(C8="","",IF(E8="マイルストーン","MILESTONE",IF(K8&gt;=1,"完了",IF(I8&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:383">
+      <c r="A9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46303</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <f>IF(OR(F9="",G9=""),"",WORKDAY.INTL(F9,G9-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="11">
+        <f>IF(OR(F9="",I9=""),"",NETWORKDAYS.INTL(F9,I9-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <f>IF(OR(H9="",J9=""),"",NETWORKDAYS.INTL(H9,J9-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
+        <v>1</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="11">
+        <f>IF(C9="","",IF(E9="マイルストーン","MILESTONE",IF(K9&gt;=1,"完了",IF(I9&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:383">
+      <c r="A10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46306</v>
+      </c>
+      <c r="G10" s="7">
         <v>30</v>
       </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>35</v>
-      </c>
-      <c r="R5" s="3">
-        <v>46296</v>
-      </c>
-      <c r="S5" s="3">
-        <v>46297</v>
-      </c>
-      <c r="T5" s="3">
-        <v>46298</v>
-      </c>
-      <c r="U5" s="3">
-        <v>46299</v>
-      </c>
-      <c r="V5" s="3">
-        <v>46300</v>
-      </c>
-      <c r="W5" s="3">
-        <v>46301</v>
-      </c>
-      <c r="X5" s="3">
-        <v>46302</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>46303</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>46304</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>46305</v>
-      </c>
-      <c r="AB5" s="3">
+      <c r="H10" s="8">
+        <f>IF(OR(F10="",G10=""),"",WORKDAY.INTL(F10,G10-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="11">
+        <f>IF(OR(F10="",I10=""),"",NETWORKDAYS.INTL(F10,I10-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="11">
+        <f>IF(OR(H10="",J10=""),"",NETWORKDAYS.INTL(H10,J10-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
+        <v>1</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="11">
+        <f>IF(C10="","",IF(E10="マイルストーン","MILESTONE",IF(K10&gt;=1,"完了",IF(I10&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:383">
+      <c r="A11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="10">
+        <v>1</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="6">
         <v>46306</v>
       </c>
-      <c r="AC5" s="3">
-        <v>46307</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>46308</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>46309</v>
-      </c>
-      <c r="AF5" s="3">
-        <v>46310</v>
-      </c>
-      <c r="AG5" s="3">
-        <v>46311</v>
-      </c>
-      <c r="AH5" s="3">
-        <v>46312</v>
-      </c>
-      <c r="AI5" s="3">
-        <v>46313</v>
-      </c>
-      <c r="AJ5" s="3">
+      <c r="G11" s="7">
+        <v>8</v>
+      </c>
+      <c r="H11" s="8">
+        <f>IF(OR(F11="",G11=""),"",WORKDAY.INTL(F11,G11-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="11">
+        <f>IF(OR(F11="",I11=""),"",NETWORKDAYS.INTL(F11,I11-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="11">
+        <f>IF(OR(H11="",J11=""),"",NETWORKDAYS.INTL(H11,J11-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
+        <v>1</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="11">
+        <f>IF(C11="","",IF(E11="マイルストーン","MILESTONE",IF(K11&gt;=1,"完了",IF(I11&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:383">
+      <c r="A12" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="6">
         <v>46314</v>
       </c>
-      <c r="AK5" s="3">
-        <v>46315</v>
-      </c>
-      <c r="AL5" s="3">
-        <v>46316</v>
-      </c>
-      <c r="AM5" s="3">
-        <v>46317</v>
-      </c>
-      <c r="AN5" s="3">
-        <v>46318</v>
-      </c>
-      <c r="AO5" s="3">
-        <v>46319</v>
-      </c>
-      <c r="AP5" s="3">
-        <v>46320</v>
-      </c>
-      <c r="AQ5" s="3">
-        <v>46321</v>
-      </c>
-      <c r="AR5" s="3">
-        <v>46322</v>
-      </c>
-      <c r="AS5" s="3">
-        <v>46323</v>
-      </c>
-      <c r="AT5" s="3">
-        <v>46324</v>
-      </c>
-      <c r="AU5" s="3">
-        <v>46325</v>
-      </c>
-      <c r="AV5" s="3">
-        <v>46326</v>
-      </c>
-      <c r="AW5" s="3">
-        <v>46327</v>
-      </c>
-      <c r="AX5" s="3">
-        <v>46328</v>
-      </c>
-      <c r="AY5" s="3">
-        <v>46329</v>
-      </c>
-      <c r="AZ5" s="3">
-        <v>46330</v>
-      </c>
-      <c r="BA5" s="3">
-        <v>46331</v>
-      </c>
-      <c r="BB5" s="3">
-        <v>46332</v>
-      </c>
-      <c r="BC5" s="3">
-        <v>46333</v>
-      </c>
-      <c r="BD5" s="3">
-        <v>46334</v>
-      </c>
-      <c r="BE5" s="3">
+      <c r="G12" s="7">
+        <v>15</v>
+      </c>
+      <c r="H12" s="8">
+        <f>IF(OR(F12="",G12=""),"",WORKDAY.INTL(F12,G12-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="11">
+        <f>IF(OR(F12="",I12=""),"",NETWORKDAYS.INTL(F12,I12-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="11">
+        <f>IF(OR(H12="",J12=""),"",NETWORKDAYS.INTL(H12,J12-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>2</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="11">
+        <f>IF(C12="","",IF(E12="マイルストーン","MILESTONE",IF(K12&gt;=1,"完了",IF(I12&lt;&gt;"","進行中","未着手"))))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:383">
+      <c r="A13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="12">
+        <v>1</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="6">
         <v>46335</v>
       </c>
-      <c r="BF5" s="3">
-        <v>46336</v>
-      </c>
-      <c r="BG5" s="3">
-        <v>46337</v>
-      </c>
-      <c r="BH5" s="3">
-        <v>46338</v>
-      </c>
-      <c r="BI5" s="3">
-        <v>46339</v>
-      </c>
-      <c r="BJ5" s="3">
-        <v>46340</v>
-      </c>
-      <c r="BK5" s="3">
-        <v>46341</v>
-      </c>
-      <c r="BL5" s="3">
-        <v>46342</v>
-      </c>
-      <c r="BM5" s="3">
-        <v>46343</v>
-      </c>
-      <c r="BN5" s="3">
-        <v>46344</v>
-      </c>
-      <c r="BO5" s="3">
-        <v>46345</v>
-      </c>
-      <c r="BP5" s="3">
-        <v>46346</v>
-      </c>
-      <c r="BQ5" s="3">
-        <v>46347</v>
-      </c>
-      <c r="BR5" s="3">
-        <v>46348</v>
-      </c>
-      <c r="BS5" s="3">
-        <v>46349</v>
-      </c>
-      <c r="BT5" s="3">
-        <v>46350</v>
-      </c>
-      <c r="BU5" s="3">
-        <v>46351</v>
-      </c>
-      <c r="BV5" s="3">
-        <v>46352</v>
-      </c>
-      <c r="BW5" s="3">
-        <v>46353</v>
-      </c>
-      <c r="BX5" s="3">
-        <v>46354</v>
-      </c>
-      <c r="BY5" s="3">
-        <v>46355</v>
-      </c>
-      <c r="BZ5" s="3">
-        <v>46356</v>
-      </c>
-      <c r="CA5" s="3">
-        <v>46357</v>
-      </c>
-      <c r="CB5" s="3">
-        <v>46358</v>
-      </c>
-      <c r="CC5" s="3">
-        <v>46359</v>
-      </c>
-      <c r="CD5" s="3">
-        <v>46360</v>
-      </c>
-      <c r="CE5" s="3">
-        <v>46361</v>
-      </c>
-      <c r="CF5" s="3">
-        <v>46362</v>
-      </c>
-      <c r="CG5" s="3">
-        <v>46363</v>
-      </c>
-      <c r="CH5" s="3">
-        <v>46364</v>
-      </c>
-      <c r="CI5" s="3">
-        <v>46365</v>
-      </c>
-      <c r="CJ5" s="3">
-        <v>46366</v>
-      </c>
-      <c r="CK5" s="3">
-        <v>46367</v>
-      </c>
-      <c r="CL5" s="3">
-        <v>46368</v>
-      </c>
-      <c r="CM5" s="3">
-        <v>46369</v>
-      </c>
-      <c r="CN5" s="3">
-        <v>46370</v>
-      </c>
-      <c r="CO5" s="3">
-        <v>46371</v>
-      </c>
-      <c r="CP5" s="3">
-        <v>46372</v>
-      </c>
-      <c r="CQ5" s="3">
-        <v>46373</v>
-      </c>
-      <c r="CR5" s="3">
-        <v>46374</v>
-      </c>
-      <c r="CS5" s="3">
-        <v>46375</v>
-      </c>
-      <c r="CT5" s="3">
-        <v>46376</v>
-      </c>
-      <c r="CU5" s="3">
-        <v>46377</v>
-      </c>
-      <c r="CV5" s="3">
-        <v>46378</v>
-      </c>
-      <c r="CW5" s="3">
-        <v>46379</v>
-      </c>
-      <c r="CX5" s="3">
-        <v>46380</v>
-      </c>
-      <c r="CY5" s="3">
-        <v>46381</v>
-      </c>
-      <c r="CZ5" s="3">
-        <v>46382</v>
-      </c>
-      <c r="DA5" s="3">
-        <v>46383</v>
-      </c>
-      <c r="DB5" s="3">
-        <v>46384</v>
-      </c>
-      <c r="DC5" s="3">
-        <v>46385</v>
-      </c>
-      <c r="DD5" s="3">
-        <v>46386</v>
-      </c>
-      <c r="DE5" s="3">
-        <v>46387</v>
-      </c>
-      <c r="DF5" s="3">
-        <v>46388</v>
-      </c>
-      <c r="DG5" s="3">
-        <v>46389</v>
-      </c>
-      <c r="DH5" s="3">
-        <v>46390</v>
-      </c>
-      <c r="DI5" s="3">
-        <v>46391</v>
-      </c>
-      <c r="DJ5" s="3">
-        <v>46392</v>
-      </c>
-      <c r="DK5" s="3">
-        <v>46393</v>
-      </c>
-      <c r="DL5" s="3">
-        <v>46394</v>
-      </c>
-      <c r="DM5" s="3">
-        <v>46395</v>
-      </c>
-      <c r="DN5" s="3">
-        <v>46396</v>
-      </c>
-      <c r="DO5" s="3">
-        <v>46397</v>
-      </c>
-      <c r="DP5" s="3">
-        <v>46398</v>
-      </c>
-      <c r="DQ5" s="3">
-        <v>46399</v>
-      </c>
-      <c r="DR5" s="3">
-        <v>46400</v>
-      </c>
-      <c r="DS5" s="3">
-        <v>46401</v>
-      </c>
-      <c r="DT5" s="3">
-        <v>46402</v>
-      </c>
-      <c r="DU5" s="3">
-        <v>46403</v>
-      </c>
-      <c r="DV5" s="3">
-        <v>46404</v>
-      </c>
-      <c r="DW5" s="3">
-        <v>46405</v>
-      </c>
-      <c r="DX5" s="3">
-        <v>46406</v>
-      </c>
-      <c r="DY5" s="3">
-        <v>46407</v>
-      </c>
-      <c r="DZ5" s="3">
-        <v>46408</v>
-      </c>
-      <c r="EA5" s="3">
-        <v>46409</v>
-      </c>
-      <c r="EB5" s="3">
-        <v>46410</v>
-      </c>
-      <c r="EC5" s="3">
-        <v>46411</v>
-      </c>
-      <c r="ED5" s="3">
-        <v>46412</v>
-      </c>
-      <c r="EE5" s="3">
-        <v>46413</v>
-      </c>
-      <c r="EF5" s="3">
-        <v>46414</v>
-      </c>
-      <c r="EG5" s="3">
-        <v>46415</v>
-      </c>
-    </row>
-    <row r="6" spans="1:137">
-      <c r="A6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46296</v>
-      </c>
-      <c r="G6" s="6">
-        <v>10</v>
-      </c>
-      <c r="H6" s="7">
-        <f>IF(OR(F6="",G6=""),"",WORKDAY.INTL(F6,G6-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="10">
-        <f>IF(OR(F6="",I6=""),"",NETWORKDAYS.INTL(F6,I6-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <f>IF(OR(H6="",J6=""),"",NETWORKDAYS.INTL(H6,J6-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="G13" s="7">
         <v>1</v>
       </c>
-      <c r="P6" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="10">
-        <f>IF(C6="","",IF(E6="マイルストーン","MILESTONE",IF(K6&gt;=1,"完了",IF(I6&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:137">
-      <c r="A7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="H13" s="8">
+        <f>IF(OR(F13="",G13=""),"",WORKDAY.INTL(F13,G13-1,1,休日!$A$4:$A$200))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="11">
+        <f>IF(OR(F13="",I13=""),"",NETWORKDAYS.INTL(F13,I13-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="11">
+        <f>IF(OR(H13="",J13=""),"",NETWORKDAYS.INTL(H13,J13-1,1,休日!$A$4:$A$200)-1)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46296</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7">
-        <f>IF(OR(F7="",G7=""),"",WORKDAY.INTL(F7,G7-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="10">
-        <f>IF(OR(F7="",I7=""),"",NETWORKDAYS.INTL(F7,I7-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <f>IF(OR(H7="",J7=""),"",NETWORKDAYS.INTL(H7,J7-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="6">
-        <v>1</v>
-      </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="10">
-        <f>IF(C7="","",IF(E7="マイルストーン","MILESTONE",IF(K7&gt;=1,"完了",IF(I7&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:137">
-      <c r="A8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="9">
-        <v>1</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="5">
-        <v>46297</v>
-      </c>
-      <c r="G8" s="6">
-        <v>5</v>
-      </c>
-      <c r="H8" s="7">
-        <f>IF(OR(F8="",G8=""),"",WORKDAY.INTL(F8,G8-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="10">
-        <f>IF(OR(F8="",I8=""),"",NETWORKDAYS.INTL(F8,I8-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <f>IF(OR(H8="",J8=""),"",NETWORKDAYS.INTL(H8,J8-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>1</v>
-      </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="10">
-        <f>IF(C8="","",IF(E8="マイルストーン","MILESTONE",IF(K8&gt;=1,"完了",IF(I8&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:137">
-      <c r="A9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="11">
-        <v>1</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="5">
-        <v>46303</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7">
-        <f>IF(OR(F9="",G9=""),"",WORKDAY.INTL(F9,G9-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" s="10">
-        <f>IF(OR(F9="",I9=""),"",NETWORKDAYS.INTL(F9,I9-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="10">
-        <f>IF(OR(H9="",J9=""),"",NETWORKDAYS.INTL(H9,J9-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="6">
-        <v>1</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="10">
-        <f>IF(C9="","",IF(E9="マイルストーン","MILESTONE",IF(K9&gt;=1,"完了",IF(I9&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:137">
-      <c r="A10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="5">
-        <v>46306</v>
-      </c>
-      <c r="G10" s="6">
-        <v>30</v>
-      </c>
-      <c r="H10" s="7">
-        <f>IF(OR(F10="",G10=""),"",WORKDAY.INTL(F10,G10-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="10">
-        <f>IF(OR(F10="",I10=""),"",NETWORKDAYS.INTL(F10,I10-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="10">
-        <f>IF(OR(H10="",J10=""),"",NETWORKDAYS.INTL(H10,J10-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="6">
-        <v>1</v>
-      </c>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="10">
-        <f>IF(C10="","",IF(E10="マイルストーン","MILESTONE",IF(K10&gt;=1,"完了",IF(I10&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:137">
-      <c r="A11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46306</v>
-      </c>
-      <c r="G11" s="6">
-        <v>8</v>
-      </c>
-      <c r="H11" s="7">
-        <f>IF(OR(F11="",G11=""),"",WORKDAY.INTL(F11,G11-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="10">
-        <f>IF(OR(F11="",I11=""),"",NETWORKDAYS.INTL(F11,I11-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <f>IF(OR(H11="",J11=""),"",NETWORKDAYS.INTL(H11,J11-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="6">
-        <v>1</v>
-      </c>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10">
-        <f>IF(C11="","",IF(E11="マイルストーン","MILESTONE",IF(K11&gt;=1,"完了",IF(I11&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:137">
-      <c r="A12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="9">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="5">
-        <v>46314</v>
-      </c>
-      <c r="G12" s="6">
-        <v>15</v>
-      </c>
-      <c r="H12" s="7">
-        <f>IF(OR(F12="",G12=""),"",WORKDAY.INTL(F12,G12-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="10">
-        <f>IF(OR(F12="",I12=""),"",NETWORKDAYS.INTL(F12,I12-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="10">
-        <f>IF(OR(H12="",J12=""),"",NETWORKDAYS.INTL(H12,J12-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="6">
-        <v>2</v>
-      </c>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="10">
-        <f>IF(C12="","",IF(E12="マイルストーン","MILESTONE",IF(K12&gt;=1,"完了",IF(I12&lt;&gt;"","進行中","未着手"))))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:137">
-      <c r="A13" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="11">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="5">
-        <v>46335</v>
-      </c>
-      <c r="G13" s="6">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7">
-        <f>IF(OR(F13="",G13=""),"",WORKDAY.INTL(F13,G13-1,1,休日!$A$4:$A$200))</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="10">
-        <f>IF(OR(F13="",I13=""),"",NETWORKDAYS.INTL(F13,I13-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="10">
-        <f>IF(OR(H13="",J13=""),"",NETWORKDAYS.INTL(H13,J13-1,1,休日!$A$4:$A$200)-1)</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="6">
-        <v>1</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="10">
+      <c r="P13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="11">
         <f>IF(C13="","",IF(E13="マイルストーン","MILESTONE",IF(K13&gt;=1,"完了",IF(I13&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:137">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="H14" s="7">
+    <row r="14" spans="1:383">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="H14" s="8">
         <f>IF(OR(F14="",G14=""),"",WORKDAY.INTL(F14,G14-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="10">
+      <c r="L14" s="10"/>
+      <c r="M14" s="11">
         <f>IF(OR(F14="",I14=""),"",NETWORKDAYS.INTL(F14,I14-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="11">
         <f>IF(OR(H14="",J14=""),"",NETWORKDAYS.INTL(H14,J14-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="10">
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11">
         <f>IF(C14="","",IF(E14="マイルストーン","MILESTONE",IF(K14&gt;=1,"完了",IF(I14&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:137">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="H15" s="7">
+    <row r="15" spans="1:383">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="H15" s="8">
         <f>IF(OR(F15="",G15=""),"",WORKDAY.INTL(F15,G15-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="10">
+      <c r="L15" s="10"/>
+      <c r="M15" s="11">
         <f>IF(OR(F15="",I15=""),"",NETWORKDAYS.INTL(F15,I15-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="11">
         <f>IF(OR(H15="",J15=""),"",NETWORKDAYS.INTL(H15,J15-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="10">
+      <c r="P15" s="10"/>
+      <c r="Q15" s="11">
         <f>IF(C15="","",IF(E15="マイルストーン","MILESTONE",IF(K15&gt;=1,"完了",IF(I15&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:137">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="H16" s="7">
+    <row r="16" spans="1:383">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="H16" s="8">
         <f>IF(OR(F16="",G16=""),"",WORKDAY.INTL(F16,G16-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="10">
+      <c r="L16" s="10"/>
+      <c r="M16" s="11">
         <f>IF(OR(F16="",I16=""),"",NETWORKDAYS.INTL(F16,I16-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="11">
         <f>IF(OR(H16="",J16=""),"",NETWORKDAYS.INTL(H16,J16-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="10">
+      <c r="P16" s="10"/>
+      <c r="Q16" s="11">
         <f>IF(C16="","",IF(E16="マイルストーン","MILESTONE",IF(K16&gt;=1,"完了",IF(I16&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="H17" s="7">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="H17" s="8">
         <f>IF(OR(F17="",G17=""),"",WORKDAY.INTL(F17,G17-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="10">
+      <c r="L17" s="10"/>
+      <c r="M17" s="11">
         <f>IF(OR(F17="",I17=""),"",NETWORKDAYS.INTL(F17,I17-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="11">
         <f>IF(OR(H17="",J17=""),"",NETWORKDAYS.INTL(H17,J17-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="10">
+      <c r="P17" s="10"/>
+      <c r="Q17" s="11">
         <f>IF(C17="","",IF(E17="マイルストーン","MILESTONE",IF(K17&gt;=1,"完了",IF(I17&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="H18" s="7">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="H18" s="8">
         <f>IF(OR(F18="",G18=""),"",WORKDAY.INTL(F18,G18-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="10">
+      <c r="L18" s="10"/>
+      <c r="M18" s="11">
         <f>IF(OR(F18="",I18=""),"",NETWORKDAYS.INTL(F18,I18-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="11">
         <f>IF(OR(H18="",J18=""),"",NETWORKDAYS.INTL(H18,J18-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="10">
+      <c r="P18" s="10"/>
+      <c r="Q18" s="11">
         <f>IF(C18="","",IF(E18="マイルストーン","MILESTONE",IF(K18&gt;=1,"完了",IF(I18&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="H19" s="7">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="H19" s="8">
         <f>IF(OR(F19="",G19=""),"",WORKDAY.INTL(F19,G19-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="10">
+      <c r="L19" s="10"/>
+      <c r="M19" s="11">
         <f>IF(OR(F19="",I19=""),"",NETWORKDAYS.INTL(F19,I19-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="11">
         <f>IF(OR(H19="",J19=""),"",NETWORKDAYS.INTL(H19,J19-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="10">
+      <c r="P19" s="10"/>
+      <c r="Q19" s="11">
         <f>IF(C19="","",IF(E19="マイルストーン","MILESTONE",IF(K19&gt;=1,"完了",IF(I19&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="H20" s="7">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="H20" s="8">
         <f>IF(OR(F20="",G20=""),"",WORKDAY.INTL(F20,G20-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="10">
+      <c r="L20" s="10"/>
+      <c r="M20" s="11">
         <f>IF(OR(F20="",I20=""),"",NETWORKDAYS.INTL(F20,I20-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="11">
         <f>IF(OR(H20="",J20=""),"",NETWORKDAYS.INTL(H20,J20-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="10">
+      <c r="P20" s="10"/>
+      <c r="Q20" s="11">
         <f>IF(C20="","",IF(E20="マイルストーン","MILESTONE",IF(K20&gt;=1,"完了",IF(I20&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="H21" s="7">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="H21" s="8">
         <f>IF(OR(F21="",G21=""),"",WORKDAY.INTL(F21,G21-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="10">
+      <c r="L21" s="10"/>
+      <c r="M21" s="11">
         <f>IF(OR(F21="",I21=""),"",NETWORKDAYS.INTL(F21,I21-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="11">
         <f>IF(OR(H21="",J21=""),"",NETWORKDAYS.INTL(H21,J21-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="10">
+      <c r="P21" s="10"/>
+      <c r="Q21" s="11">
         <f>IF(C21="","",IF(E21="マイルストーン","MILESTONE",IF(K21&gt;=1,"完了",IF(I21&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="H22" s="7">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="H22" s="8">
         <f>IF(OR(F22="",G22=""),"",WORKDAY.INTL(F22,G22-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="10">
+      <c r="L22" s="10"/>
+      <c r="M22" s="11">
         <f>IF(OR(F22="",I22=""),"",NETWORKDAYS.INTL(F22,I22-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="11">
         <f>IF(OR(H22="",J22=""),"",NETWORKDAYS.INTL(H22,J22-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="10">
+      <c r="P22" s="10"/>
+      <c r="Q22" s="11">
         <f>IF(C22="","",IF(E22="マイルストーン","MILESTONE",IF(K22&gt;=1,"完了",IF(I22&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="H23" s="7">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="H23" s="8">
         <f>IF(OR(F23="",G23=""),"",WORKDAY.INTL(F23,G23-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="10">
+      <c r="L23" s="10"/>
+      <c r="M23" s="11">
         <f>IF(OR(F23="",I23=""),"",NETWORKDAYS.INTL(F23,I23-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="11">
         <f>IF(OR(H23="",J23=""),"",NETWORKDAYS.INTL(H23,J23-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="10">
+      <c r="P23" s="10"/>
+      <c r="Q23" s="11">
         <f>IF(C23="","",IF(E23="マイルストーン","MILESTONE",IF(K23&gt;=1,"完了",IF(I23&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="H24" s="7">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="H24" s="8">
         <f>IF(OR(F24="",G24=""),"",WORKDAY.INTL(F24,G24-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="9"/>
-      <c r="M24" s="10">
+      <c r="L24" s="10"/>
+      <c r="M24" s="11">
         <f>IF(OR(F24="",I24=""),"",NETWORKDAYS.INTL(F24,I24-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="11">
         <f>IF(OR(H24="",J24=""),"",NETWORKDAYS.INTL(H24,J24-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="10">
+      <c r="P24" s="10"/>
+      <c r="Q24" s="11">
         <f>IF(C24="","",IF(E24="マイルストーン","MILESTONE",IF(K24&gt;=1,"完了",IF(I24&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="H25" s="7">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="H25" s="8">
         <f>IF(OR(F25="",G25=""),"",WORKDAY.INTL(F25,G25-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="10">
+      <c r="L25" s="10"/>
+      <c r="M25" s="11">
         <f>IF(OR(F25="",I25=""),"",NETWORKDAYS.INTL(F25,I25-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="11">
         <f>IF(OR(H25="",J25=""),"",NETWORKDAYS.INTL(H25,J25-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="10">
+      <c r="P25" s="10"/>
+      <c r="Q25" s="11">
         <f>IF(C25="","",IF(E25="マイルストーン","MILESTONE",IF(K25&gt;=1,"完了",IF(I25&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="H26" s="7">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="H26" s="8">
         <f>IF(OR(F26="",G26=""),"",WORKDAY.INTL(F26,G26-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L26" s="9"/>
-      <c r="M26" s="10">
+      <c r="L26" s="10"/>
+      <c r="M26" s="11">
         <f>IF(OR(F26="",I26=""),"",NETWORKDAYS.INTL(F26,I26-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="11">
         <f>IF(OR(H26="",J26=""),"",NETWORKDAYS.INTL(H26,J26-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="10">
+      <c r="P26" s="10"/>
+      <c r="Q26" s="11">
         <f>IF(C26="","",IF(E26="マイルストーン","MILESTONE",IF(K26&gt;=1,"完了",IF(I26&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="H27" s="7">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="H27" s="8">
         <f>IF(OR(F27="",G27=""),"",WORKDAY.INTL(F27,G27-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="10">
+      <c r="L27" s="10"/>
+      <c r="M27" s="11">
         <f>IF(OR(F27="",I27=""),"",NETWORKDAYS.INTL(F27,I27-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="11">
         <f>IF(OR(H27="",J27=""),"",NETWORKDAYS.INTL(H27,J27-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="10">
+      <c r="P27" s="10"/>
+      <c r="Q27" s="11">
         <f>IF(C27="","",IF(E27="マイルストーン","MILESTONE",IF(K27&gt;=1,"完了",IF(I27&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="H28" s="7">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="H28" s="8">
         <f>IF(OR(F28="",G28=""),"",WORKDAY.INTL(F28,G28-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="10">
+      <c r="L28" s="10"/>
+      <c r="M28" s="11">
         <f>IF(OR(F28="",I28=""),"",NETWORKDAYS.INTL(F28,I28-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="10">
+      <c r="N28" s="11">
         <f>IF(OR(H28="",J28=""),"",NETWORKDAYS.INTL(H28,J28-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="10">
+      <c r="P28" s="10"/>
+      <c r="Q28" s="11">
         <f>IF(C28="","",IF(E28="マイルストーン","MILESTONE",IF(K28&gt;=1,"完了",IF(I28&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="H29" s="7">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="H29" s="8">
         <f>IF(OR(F29="",G29=""),"",WORKDAY.INTL(F29,G29-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="10">
+      <c r="L29" s="10"/>
+      <c r="M29" s="11">
         <f>IF(OR(F29="",I29=""),"",NETWORKDAYS.INTL(F29,I29-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="11">
         <f>IF(OR(H29="",J29=""),"",NETWORKDAYS.INTL(H29,J29-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="10">
+      <c r="P29" s="10"/>
+      <c r="Q29" s="11">
         <f>IF(C29="","",IF(E29="マイルストーン","MILESTONE",IF(K29&gt;=1,"完了",IF(I29&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="H30" s="7">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="H30" s="8">
         <f>IF(OR(F30="",G30=""),"",WORKDAY.INTL(F30,G30-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="10">
+      <c r="L30" s="10"/>
+      <c r="M30" s="11">
         <f>IF(OR(F30="",I30=""),"",NETWORKDAYS.INTL(F30,I30-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="11">
         <f>IF(OR(H30="",J30=""),"",NETWORKDAYS.INTL(H30,J30-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="10">
+      <c r="P30" s="10"/>
+      <c r="Q30" s="11">
         <f>IF(C30="","",IF(E30="マイルストーン","MILESTONE",IF(K30&gt;=1,"完了",IF(I30&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="H31" s="7">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="H31" s="8">
         <f>IF(OR(F31="",G31=""),"",WORKDAY.INTL(F31,G31-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L31" s="9"/>
-      <c r="M31" s="10">
+      <c r="L31" s="10"/>
+      <c r="M31" s="11">
         <f>IF(OR(F31="",I31=""),"",NETWORKDAYS.INTL(F31,I31-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="11">
         <f>IF(OR(H31="",J31=""),"",NETWORKDAYS.INTL(H31,J31-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="10">
+      <c r="P31" s="10"/>
+      <c r="Q31" s="11">
         <f>IF(C31="","",IF(E31="マイルストーン","MILESTONE",IF(K31&gt;=1,"完了",IF(I31&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:17">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="H32" s="7">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="H32" s="8">
         <f>IF(OR(F32="",G32=""),"",WORKDAY.INTL(F32,G32-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="10">
+      <c r="L32" s="10"/>
+      <c r="M32" s="11">
         <f>IF(OR(F32="",I32=""),"",NETWORKDAYS.INTL(F32,I32-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="11">
         <f>IF(OR(H32="",J32=""),"",NETWORKDAYS.INTL(H32,J32-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="10">
+      <c r="P32" s="10"/>
+      <c r="Q32" s="11">
         <f>IF(C32="","",IF(E32="マイルストーン","MILESTONE",IF(K32&gt;=1,"完了",IF(I32&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="H33" s="7">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="H33" s="8">
         <f>IF(OR(F33="",G33=""),"",WORKDAY.INTL(F33,G33-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="10">
+      <c r="L33" s="10"/>
+      <c r="M33" s="11">
         <f>IF(OR(F33="",I33=""),"",NETWORKDAYS.INTL(F33,I33-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="11">
         <f>IF(OR(H33="",J33=""),"",NETWORKDAYS.INTL(H33,J33-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="10">
+      <c r="P33" s="10"/>
+      <c r="Q33" s="11">
         <f>IF(C33="","",IF(E33="マイルストーン","MILESTONE",IF(K33&gt;=1,"完了",IF(I33&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="H34" s="7">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="H34" s="8">
         <f>IF(OR(F34="",G34=""),"",WORKDAY.INTL(F34,G34-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L34" s="9"/>
-      <c r="M34" s="10">
+      <c r="L34" s="10"/>
+      <c r="M34" s="11">
         <f>IF(OR(F34="",I34=""),"",NETWORKDAYS.INTL(F34,I34-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="11">
         <f>IF(OR(H34="",J34=""),"",NETWORKDAYS.INTL(H34,J34-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="10">
+      <c r="P34" s="10"/>
+      <c r="Q34" s="11">
         <f>IF(C34="","",IF(E34="マイルストーン","MILESTONE",IF(K34&gt;=1,"完了",IF(I34&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="H35" s="7">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="H35" s="8">
         <f>IF(OR(F35="",G35=""),"",WORKDAY.INTL(F35,G35-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L35" s="9"/>
-      <c r="M35" s="10">
+      <c r="L35" s="10"/>
+      <c r="M35" s="11">
         <f>IF(OR(F35="",I35=""),"",NETWORKDAYS.INTL(F35,I35-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="11">
         <f>IF(OR(H35="",J35=""),"",NETWORKDAYS.INTL(H35,J35-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="10">
+      <c r="P35" s="10"/>
+      <c r="Q35" s="11">
         <f>IF(C35="","",IF(E35="マイルストーン","MILESTONE",IF(K35&gt;=1,"完了",IF(I35&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="H36" s="7">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="H36" s="8">
         <f>IF(OR(F36="",G36=""),"",WORKDAY.INTL(F36,G36-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="10">
+      <c r="L36" s="10"/>
+      <c r="M36" s="11">
         <f>IF(OR(F36="",I36=""),"",NETWORKDAYS.INTL(F36,I36-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="11">
         <f>IF(OR(H36="",J36=""),"",NETWORKDAYS.INTL(H36,J36-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="10">
+      <c r="P36" s="10"/>
+      <c r="Q36" s="11">
         <f>IF(C36="","",IF(E36="マイルストーン","MILESTONE",IF(K36&gt;=1,"完了",IF(I36&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="H37" s="7">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="H37" s="8">
         <f>IF(OR(F37="",G37=""),"",WORKDAY.INTL(F37,G37-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L37" s="9"/>
-      <c r="M37" s="10">
+      <c r="L37" s="10"/>
+      <c r="M37" s="11">
         <f>IF(OR(F37="",I37=""),"",NETWORKDAYS.INTL(F37,I37-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="10">
+      <c r="N37" s="11">
         <f>IF(OR(H37="",J37=""),"",NETWORKDAYS.INTL(H37,J37-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="10">
+      <c r="P37" s="10"/>
+      <c r="Q37" s="11">
         <f>IF(C37="","",IF(E37="マイルストーン","MILESTONE",IF(K37&gt;=1,"完了",IF(I37&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="H38" s="7">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="H38" s="8">
         <f>IF(OR(F38="",G38=""),"",WORKDAY.INTL(F38,G38-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="10">
+      <c r="L38" s="10"/>
+      <c r="M38" s="11">
         <f>IF(OR(F38="",I38=""),"",NETWORKDAYS.INTL(F38,I38-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="11">
         <f>IF(OR(H38="",J38=""),"",NETWORKDAYS.INTL(H38,J38-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="10">
+      <c r="P38" s="10"/>
+      <c r="Q38" s="11">
         <f>IF(C38="","",IF(E38="マイルストーン","MILESTONE",IF(K38&gt;=1,"完了",IF(I38&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="H39" s="7">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="H39" s="8">
         <f>IF(OR(F39="",G39=""),"",WORKDAY.INTL(F39,G39-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L39" s="9"/>
-      <c r="M39" s="10">
+      <c r="L39" s="10"/>
+      <c r="M39" s="11">
         <f>IF(OR(F39="",I39=""),"",NETWORKDAYS.INTL(F39,I39-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="11">
         <f>IF(OR(H39="",J39=""),"",NETWORKDAYS.INTL(H39,J39-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="10">
+      <c r="P39" s="10"/>
+      <c r="Q39" s="11">
         <f>IF(C39="","",IF(E39="マイルストーン","MILESTONE",IF(K39&gt;=1,"完了",IF(I39&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:17">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="H40" s="7">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="H40" s="8">
         <f>IF(OR(F40="",G40=""),"",WORKDAY.INTL(F40,G40-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L40" s="9"/>
-      <c r="M40" s="10">
+      <c r="L40" s="10"/>
+      <c r="M40" s="11">
         <f>IF(OR(F40="",I40=""),"",NETWORKDAYS.INTL(F40,I40-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N40" s="10">
+      <c r="N40" s="11">
         <f>IF(OR(H40="",J40=""),"",NETWORKDAYS.INTL(H40,J40-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="10">
+      <c r="P40" s="10"/>
+      <c r="Q40" s="11">
         <f>IF(C40="","",IF(E40="マイルストーン","MILESTONE",IF(K40&gt;=1,"完了",IF(I40&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="H41" s="7">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="H41" s="8">
         <f>IF(OR(F41="",G41=""),"",WORKDAY.INTL(F41,G41-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L41" s="9"/>
-      <c r="M41" s="10">
+      <c r="L41" s="10"/>
+      <c r="M41" s="11">
         <f>IF(OR(F41="",I41=""),"",NETWORKDAYS.INTL(F41,I41-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="10">
+      <c r="N41" s="11">
         <f>IF(OR(H41="",J41=""),"",NETWORKDAYS.INTL(H41,J41-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="10">
+      <c r="P41" s="10"/>
+      <c r="Q41" s="11">
         <f>IF(C41="","",IF(E41="マイルストーン","MILESTONE",IF(K41&gt;=1,"完了",IF(I41&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:17">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="H42" s="7">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="H42" s="8">
         <f>IF(OR(F42="",G42=""),"",WORKDAY.INTL(F42,G42-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="10">
+      <c r="L42" s="10"/>
+      <c r="M42" s="11">
         <f>IF(OR(F42="",I42=""),"",NETWORKDAYS.INTL(F42,I42-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="11">
         <f>IF(OR(H42="",J42=""),"",NETWORKDAYS.INTL(H42,J42-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="10">
+      <c r="P42" s="10"/>
+      <c r="Q42" s="11">
         <f>IF(C42="","",IF(E42="マイルストーン","MILESTONE",IF(K42&gt;=1,"完了",IF(I42&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="H43" s="7">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="H43" s="8">
         <f>IF(OR(F43="",G43=""),"",WORKDAY.INTL(F43,G43-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L43" s="9"/>
-      <c r="M43" s="10">
+      <c r="L43" s="10"/>
+      <c r="M43" s="11">
         <f>IF(OR(F43="",I43=""),"",NETWORKDAYS.INTL(F43,I43-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="11">
         <f>IF(OR(H43="",J43=""),"",NETWORKDAYS.INTL(H43,J43-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="10">
+      <c r="P43" s="10"/>
+      <c r="Q43" s="11">
         <f>IF(C43="","",IF(E43="マイルストーン","MILESTONE",IF(K43&gt;=1,"完了",IF(I43&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="H44" s="7">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="H44" s="8">
         <f>IF(OR(F44="",G44=""),"",WORKDAY.INTL(F44,G44-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L44" s="9"/>
-      <c r="M44" s="10">
+      <c r="L44" s="10"/>
+      <c r="M44" s="11">
         <f>IF(OR(F44="",I44=""),"",NETWORKDAYS.INTL(F44,I44-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="10">
+      <c r="N44" s="11">
         <f>IF(OR(H44="",J44=""),"",NETWORKDAYS.INTL(H44,J44-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="10">
+      <c r="P44" s="10"/>
+      <c r="Q44" s="11">
         <f>IF(C44="","",IF(E44="マイルストーン","MILESTONE",IF(K44&gt;=1,"完了",IF(I44&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="H45" s="7">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="H45" s="8">
         <f>IF(OR(F45="",G45=""),"",WORKDAY.INTL(F45,G45-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L45" s="9"/>
-      <c r="M45" s="10">
+      <c r="L45" s="10"/>
+      <c r="M45" s="11">
         <f>IF(OR(F45="",I45=""),"",NETWORKDAYS.INTL(F45,I45-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="11">
         <f>IF(OR(H45="",J45=""),"",NETWORKDAYS.INTL(H45,J45-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="10">
+      <c r="P45" s="10"/>
+      <c r="Q45" s="11">
         <f>IF(C45="","",IF(E45="マイルストーン","MILESTONE",IF(K45&gt;=1,"完了",IF(I45&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="H46" s="7">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="H46" s="8">
         <f>IF(OR(F46="",G46=""),"",WORKDAY.INTL(F46,G46-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L46" s="9"/>
-      <c r="M46" s="10">
+      <c r="L46" s="10"/>
+      <c r="M46" s="11">
         <f>IF(OR(F46="",I46=""),"",NETWORKDAYS.INTL(F46,I46-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="10">
+      <c r="N46" s="11">
         <f>IF(OR(H46="",J46=""),"",NETWORKDAYS.INTL(H46,J46-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="10">
+      <c r="P46" s="10"/>
+      <c r="Q46" s="11">
         <f>IF(C46="","",IF(E46="マイルストーン","MILESTONE",IF(K46&gt;=1,"完了",IF(I46&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="H47" s="7">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="H47" s="8">
         <f>IF(OR(F47="",G47=""),"",WORKDAY.INTL(F47,G47-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="10">
+      <c r="L47" s="10"/>
+      <c r="M47" s="11">
         <f>IF(OR(F47="",I47=""),"",NETWORKDAYS.INTL(F47,I47-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="11">
         <f>IF(OR(H47="",J47=""),"",NETWORKDAYS.INTL(H47,J47-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="10">
+      <c r="P47" s="10"/>
+      <c r="Q47" s="11">
         <f>IF(C47="","",IF(E47="マイルストーン","MILESTONE",IF(K47&gt;=1,"完了",IF(I47&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="H48" s="7">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="H48" s="8">
         <f>IF(OR(F48="",G48=""),"",WORKDAY.INTL(F48,G48-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L48" s="9"/>
-      <c r="M48" s="10">
+      <c r="L48" s="10"/>
+      <c r="M48" s="11">
         <f>IF(OR(F48="",I48=""),"",NETWORKDAYS.INTL(F48,I48-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N48" s="10">
+      <c r="N48" s="11">
         <f>IF(OR(H48="",J48=""),"",NETWORKDAYS.INTL(H48,J48-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="10">
+      <c r="P48" s="10"/>
+      <c r="Q48" s="11">
         <f>IF(C48="","",IF(E48="マイルストーン","MILESTONE",IF(K48&gt;=1,"完了",IF(I48&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:17">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="H49" s="7">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="H49" s="8">
         <f>IF(OR(F49="",G49=""),"",WORKDAY.INTL(F49,G49-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="10">
+      <c r="L49" s="10"/>
+      <c r="M49" s="11">
         <f>IF(OR(F49="",I49=""),"",NETWORKDAYS.INTL(F49,I49-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N49" s="10">
+      <c r="N49" s="11">
         <f>IF(OR(H49="",J49=""),"",NETWORKDAYS.INTL(H49,J49-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P49" s="9"/>
-      <c r="Q49" s="10">
+      <c r="P49" s="10"/>
+      <c r="Q49" s="11">
         <f>IF(C49="","",IF(E49="マイルストーン","MILESTONE",IF(K49&gt;=1,"完了",IF(I49&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:17">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="H50" s="7">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="H50" s="8">
         <f>IF(OR(F50="",G50=""),"",WORKDAY.INTL(F50,G50-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="10">
+      <c r="L50" s="10"/>
+      <c r="M50" s="11">
         <f>IF(OR(F50="",I50=""),"",NETWORKDAYS.INTL(F50,I50-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N50" s="10">
+      <c r="N50" s="11">
         <f>IF(OR(H50="",J50=""),"",NETWORKDAYS.INTL(H50,J50-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P50" s="9"/>
-      <c r="Q50" s="10">
+      <c r="P50" s="10"/>
+      <c r="Q50" s="11">
         <f>IF(C50="","",IF(E50="マイルストーン","MILESTONE",IF(K50&gt;=1,"完了",IF(I50&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:17">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="H51" s="7">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="H51" s="8">
         <f>IF(OR(F51="",G51=""),"",WORKDAY.INTL(F51,G51-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L51" s="9"/>
-      <c r="M51" s="10">
+      <c r="L51" s="10"/>
+      <c r="M51" s="11">
         <f>IF(OR(F51="",I51=""),"",NETWORKDAYS.INTL(F51,I51-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N51" s="10">
+      <c r="N51" s="11">
         <f>IF(OR(H51="",J51=""),"",NETWORKDAYS.INTL(H51,J51-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="10">
+      <c r="P51" s="10"/>
+      <c r="Q51" s="11">
         <f>IF(C51="","",IF(E51="マイルストーン","MILESTONE",IF(K51&gt;=1,"完了",IF(I51&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:17">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="H52" s="7">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="H52" s="8">
         <f>IF(OR(F52="",G52=""),"",WORKDAY.INTL(F52,G52-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L52" s="9"/>
-      <c r="M52" s="10">
+      <c r="L52" s="10"/>
+      <c r="M52" s="11">
         <f>IF(OR(F52="",I52=""),"",NETWORKDAYS.INTL(F52,I52-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N52" s="10">
+      <c r="N52" s="11">
         <f>IF(OR(H52="",J52=""),"",NETWORKDAYS.INTL(H52,J52-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P52" s="9"/>
-      <c r="Q52" s="10">
+      <c r="P52" s="10"/>
+      <c r="Q52" s="11">
         <f>IF(C52="","",IF(E52="マイルストーン","MILESTONE",IF(K52&gt;=1,"完了",IF(I52&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="H53" s="7">
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="H53" s="8">
         <f>IF(OR(F53="",G53=""),"",WORKDAY.INTL(F53,G53-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L53" s="9"/>
-      <c r="M53" s="10">
+      <c r="L53" s="10"/>
+      <c r="M53" s="11">
         <f>IF(OR(F53="",I53=""),"",NETWORKDAYS.INTL(F53,I53-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N53" s="10">
+      <c r="N53" s="11">
         <f>IF(OR(H53="",J53=""),"",NETWORKDAYS.INTL(H53,J53-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="10">
+      <c r="P53" s="10"/>
+      <c r="Q53" s="11">
         <f>IF(C53="","",IF(E53="マイルストーン","MILESTONE",IF(K53&gt;=1,"完了",IF(I53&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:17">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="H54" s="7">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="H54" s="8">
         <f>IF(OR(F54="",G54=""),"",WORKDAY.INTL(F54,G54-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L54" s="9"/>
-      <c r="M54" s="10">
+      <c r="L54" s="10"/>
+      <c r="M54" s="11">
         <f>IF(OR(F54="",I54=""),"",NETWORKDAYS.INTL(F54,I54-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="10">
+      <c r="N54" s="11">
         <f>IF(OR(H54="",J54=""),"",NETWORKDAYS.INTL(H54,J54-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P54" s="9"/>
-      <c r="Q54" s="10">
+      <c r="P54" s="10"/>
+      <c r="Q54" s="11">
         <f>IF(C54="","",IF(E54="マイルストーン","MILESTONE",IF(K54&gt;=1,"完了",IF(I54&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:17">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="H55" s="7">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="H55" s="8">
         <f>IF(OR(F55="",G55=""),"",WORKDAY.INTL(F55,G55-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L55" s="9"/>
-      <c r="M55" s="10">
+      <c r="L55" s="10"/>
+      <c r="M55" s="11">
         <f>IF(OR(F55="",I55=""),"",NETWORKDAYS.INTL(F55,I55-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N55" s="10">
+      <c r="N55" s="11">
         <f>IF(OR(H55="",J55=""),"",NETWORKDAYS.INTL(H55,J55-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P55" s="9"/>
-      <c r="Q55" s="10">
+      <c r="P55" s="10"/>
+      <c r="Q55" s="11">
         <f>IF(C55="","",IF(E55="マイルストーン","MILESTONE",IF(K55&gt;=1,"完了",IF(I55&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:17">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="H56" s="7">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="H56" s="8">
         <f>IF(OR(F56="",G56=""),"",WORKDAY.INTL(F56,G56-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L56" s="9"/>
-      <c r="M56" s="10">
+      <c r="L56" s="10"/>
+      <c r="M56" s="11">
         <f>IF(OR(F56="",I56=""),"",NETWORKDAYS.INTL(F56,I56-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N56" s="10">
+      <c r="N56" s="11">
         <f>IF(OR(H56="",J56=""),"",NETWORKDAYS.INTL(H56,J56-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P56" s="9"/>
-      <c r="Q56" s="10">
+      <c r="P56" s="10"/>
+      <c r="Q56" s="11">
         <f>IF(C56="","",IF(E56="マイルストーン","MILESTONE",IF(K56&gt;=1,"完了",IF(I56&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:17">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="H57" s="7">
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="H57" s="8">
         <f>IF(OR(F57="",G57=""),"",WORKDAY.INTL(F57,G57-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L57" s="9"/>
-      <c r="M57" s="10">
+      <c r="L57" s="10"/>
+      <c r="M57" s="11">
         <f>IF(OR(F57="",I57=""),"",NETWORKDAYS.INTL(F57,I57-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N57" s="10">
+      <c r="N57" s="11">
         <f>IF(OR(H57="",J57=""),"",NETWORKDAYS.INTL(H57,J57-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P57" s="9"/>
-      <c r="Q57" s="10">
+      <c r="P57" s="10"/>
+      <c r="Q57" s="11">
         <f>IF(C57="","",IF(E57="マイルストーン","MILESTONE",IF(K57&gt;=1,"完了",IF(I57&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:17">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="H58" s="7">
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="H58" s="8">
         <f>IF(OR(F58="",G58=""),"",WORKDAY.INTL(F58,G58-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L58" s="9"/>
-      <c r="M58" s="10">
+      <c r="L58" s="10"/>
+      <c r="M58" s="11">
         <f>IF(OR(F58="",I58=""),"",NETWORKDAYS.INTL(F58,I58-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N58" s="10">
+      <c r="N58" s="11">
         <f>IF(OR(H58="",J58=""),"",NETWORKDAYS.INTL(H58,J58-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="10">
+      <c r="P58" s="10"/>
+      <c r="Q58" s="11">
         <f>IF(C58="","",IF(E58="マイルストーン","MILESTONE",IF(K58&gt;=1,"完了",IF(I58&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:17">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="H59" s="7">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="H59" s="8">
         <f>IF(OR(F59="",G59=""),"",WORKDAY.INTL(F59,G59-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L59" s="9"/>
-      <c r="M59" s="10">
+      <c r="L59" s="10"/>
+      <c r="M59" s="11">
         <f>IF(OR(F59="",I59=""),"",NETWORKDAYS.INTL(F59,I59-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="10">
+      <c r="N59" s="11">
         <f>IF(OR(H59="",J59=""),"",NETWORKDAYS.INTL(H59,J59-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P59" s="9"/>
-      <c r="Q59" s="10">
+      <c r="P59" s="10"/>
+      <c r="Q59" s="11">
         <f>IF(C59="","",IF(E59="マイルストーン","MILESTONE",IF(K59&gt;=1,"完了",IF(I59&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:17">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="H60" s="7">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="H60" s="8">
         <f>IF(OR(F60="",G60=""),"",WORKDAY.INTL(F60,G60-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L60" s="9"/>
-      <c r="M60" s="10">
+      <c r="L60" s="10"/>
+      <c r="M60" s="11">
         <f>IF(OR(F60="",I60=""),"",NETWORKDAYS.INTL(F60,I60-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N60" s="10">
+      <c r="N60" s="11">
         <f>IF(OR(H60="",J60=""),"",NETWORKDAYS.INTL(H60,J60-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P60" s="9"/>
-      <c r="Q60" s="10">
+      <c r="P60" s="10"/>
+      <c r="Q60" s="11">
         <f>IF(C60="","",IF(E60="マイルストーン","MILESTONE",IF(K60&gt;=1,"完了",IF(I60&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:17">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="H61" s="7">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="H61" s="8">
         <f>IF(OR(F61="",G61=""),"",WORKDAY.INTL(F61,G61-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L61" s="9"/>
-      <c r="M61" s="10">
+      <c r="L61" s="10"/>
+      <c r="M61" s="11">
         <f>IF(OR(F61="",I61=""),"",NETWORKDAYS.INTL(F61,I61-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N61" s="11">
         <f>IF(OR(H61="",J61=""),"",NETWORKDAYS.INTL(H61,J61-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P61" s="9"/>
-      <c r="Q61" s="10">
+      <c r="P61" s="10"/>
+      <c r="Q61" s="11">
         <f>IF(C61="","",IF(E61="マイルストーン","MILESTONE",IF(K61&gt;=1,"完了",IF(I61&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:17">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="H62" s="7">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="H62" s="8">
         <f>IF(OR(F62="",G62=""),"",WORKDAY.INTL(F62,G62-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L62" s="9"/>
-      <c r="M62" s="10">
+      <c r="L62" s="10"/>
+      <c r="M62" s="11">
         <f>IF(OR(F62="",I62=""),"",NETWORKDAYS.INTL(F62,I62-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N62" s="10">
+      <c r="N62" s="11">
         <f>IF(OR(H62="",J62=""),"",NETWORKDAYS.INTL(H62,J62-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P62" s="9"/>
-      <c r="Q62" s="10">
+      <c r="P62" s="10"/>
+      <c r="Q62" s="11">
         <f>IF(C62="","",IF(E62="マイルストーン","MILESTONE",IF(K62&gt;=1,"完了",IF(I62&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:17">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="H63" s="7">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="H63" s="8">
         <f>IF(OR(F63="",G63=""),"",WORKDAY.INTL(F63,G63-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L63" s="9"/>
-      <c r="M63" s="10">
+      <c r="L63" s="10"/>
+      <c r="M63" s="11">
         <f>IF(OR(F63="",I63=""),"",NETWORKDAYS.INTL(F63,I63-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N63" s="10">
+      <c r="N63" s="11">
         <f>IF(OR(H63="",J63=""),"",NETWORKDAYS.INTL(H63,J63-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P63" s="9"/>
-      <c r="Q63" s="10">
+      <c r="P63" s="10"/>
+      <c r="Q63" s="11">
         <f>IF(C63="","",IF(E63="マイルストーン","MILESTONE",IF(K63&gt;=1,"完了",IF(I63&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:17">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="H64" s="7">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="H64" s="8">
         <f>IF(OR(F64="",G64=""),"",WORKDAY.INTL(F64,G64-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L64" s="9"/>
-      <c r="M64" s="10">
+      <c r="L64" s="10"/>
+      <c r="M64" s="11">
         <f>IF(OR(F64="",I64=""),"",NETWORKDAYS.INTL(F64,I64-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N64" s="10">
+      <c r="N64" s="11">
         <f>IF(OR(H64="",J64=""),"",NETWORKDAYS.INTL(H64,J64-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P64" s="9"/>
-      <c r="Q64" s="10">
+      <c r="P64" s="10"/>
+      <c r="Q64" s="11">
         <f>IF(C64="","",IF(E64="マイルストーン","MILESTONE",IF(K64&gt;=1,"完了",IF(I64&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="H65" s="7">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="H65" s="8">
         <f>IF(OR(F65="",G65=""),"",WORKDAY.INTL(F65,G65-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L65" s="9"/>
-      <c r="M65" s="10">
+      <c r="L65" s="10"/>
+      <c r="M65" s="11">
         <f>IF(OR(F65="",I65=""),"",NETWORKDAYS.INTL(F65,I65-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N65" s="10">
+      <c r="N65" s="11">
         <f>IF(OR(H65="",J65=""),"",NETWORKDAYS.INTL(H65,J65-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P65" s="9"/>
-      <c r="Q65" s="10">
+      <c r="P65" s="10"/>
+      <c r="Q65" s="11">
         <f>IF(C65="","",IF(E65="マイルストーン","MILESTONE",IF(K65&gt;=1,"完了",IF(I65&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:17">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="H66" s="7">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="H66" s="8">
         <f>IF(OR(F66="",G66=""),"",WORKDAY.INTL(F66,G66-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L66" s="9"/>
-      <c r="M66" s="10">
+      <c r="L66" s="10"/>
+      <c r="M66" s="11">
         <f>IF(OR(F66="",I66=""),"",NETWORKDAYS.INTL(F66,I66-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N66" s="10">
+      <c r="N66" s="11">
         <f>IF(OR(H66="",J66=""),"",NETWORKDAYS.INTL(H66,J66-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P66" s="9"/>
-      <c r="Q66" s="10">
+      <c r="P66" s="10"/>
+      <c r="Q66" s="11">
         <f>IF(C66="","",IF(E66="マイルストーン","MILESTONE",IF(K66&gt;=1,"完了",IF(I66&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:17">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="H67" s="7">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="H67" s="8">
         <f>IF(OR(F67="",G67=""),"",WORKDAY.INTL(F67,G67-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L67" s="9"/>
-      <c r="M67" s="10">
+      <c r="L67" s="10"/>
+      <c r="M67" s="11">
         <f>IF(OR(F67="",I67=""),"",NETWORKDAYS.INTL(F67,I67-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N67" s="10">
+      <c r="N67" s="11">
         <f>IF(OR(H67="",J67=""),"",NETWORKDAYS.INTL(H67,J67-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P67" s="9"/>
-      <c r="Q67" s="10">
+      <c r="P67" s="10"/>
+      <c r="Q67" s="11">
         <f>IF(C67="","",IF(E67="マイルストーン","MILESTONE",IF(K67&gt;=1,"完了",IF(I67&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:17">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="H68" s="7">
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="H68" s="8">
         <f>IF(OR(F68="",G68=""),"",WORKDAY.INTL(F68,G68-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L68" s="9"/>
-      <c r="M68" s="10">
+      <c r="L68" s="10"/>
+      <c r="M68" s="11">
         <f>IF(OR(F68="",I68=""),"",NETWORKDAYS.INTL(F68,I68-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N68" s="10">
+      <c r="N68" s="11">
         <f>IF(OR(H68="",J68=""),"",NETWORKDAYS.INTL(H68,J68-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P68" s="9"/>
-      <c r="Q68" s="10">
+      <c r="P68" s="10"/>
+      <c r="Q68" s="11">
         <f>IF(C68="","",IF(E68="マイルストーン","MILESTONE",IF(K68&gt;=1,"完了",IF(I68&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:17">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="H69" s="7">
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="H69" s="8">
         <f>IF(OR(F69="",G69=""),"",WORKDAY.INTL(F69,G69-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L69" s="9"/>
-      <c r="M69" s="10">
+      <c r="L69" s="10"/>
+      <c r="M69" s="11">
         <f>IF(OR(F69="",I69=""),"",NETWORKDAYS.INTL(F69,I69-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N69" s="10">
+      <c r="N69" s="11">
         <f>IF(OR(H69="",J69=""),"",NETWORKDAYS.INTL(H69,J69-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P69" s="9"/>
-      <c r="Q69" s="10">
+      <c r="P69" s="10"/>
+      <c r="Q69" s="11">
         <f>IF(C69="","",IF(E69="マイルストーン","MILESTONE",IF(K69&gt;=1,"完了",IF(I69&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:17">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="H70" s="7">
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="H70" s="8">
         <f>IF(OR(F70="",G70=""),"",WORKDAY.INTL(F70,G70-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L70" s="9"/>
-      <c r="M70" s="10">
+      <c r="L70" s="10"/>
+      <c r="M70" s="11">
         <f>IF(OR(F70="",I70=""),"",NETWORKDAYS.INTL(F70,I70-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N70" s="10">
+      <c r="N70" s="11">
         <f>IF(OR(H70="",J70=""),"",NETWORKDAYS.INTL(H70,J70-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P70" s="9"/>
-      <c r="Q70" s="10">
+      <c r="P70" s="10"/>
+      <c r="Q70" s="11">
         <f>IF(C70="","",IF(E70="マイルストーン","MILESTONE",IF(K70&gt;=1,"完了",IF(I70&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:17">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="H71" s="7">
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="H71" s="8">
         <f>IF(OR(F71="",G71=""),"",WORKDAY.INTL(F71,G71-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L71" s="9"/>
-      <c r="M71" s="10">
+      <c r="L71" s="10"/>
+      <c r="M71" s="11">
         <f>IF(OR(F71="",I71=""),"",NETWORKDAYS.INTL(F71,I71-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N71" s="10">
+      <c r="N71" s="11">
         <f>IF(OR(H71="",J71=""),"",NETWORKDAYS.INTL(H71,J71-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P71" s="9"/>
-      <c r="Q71" s="10">
+      <c r="P71" s="10"/>
+      <c r="Q71" s="11">
         <f>IF(C71="","",IF(E71="マイルストーン","MILESTONE",IF(K71&gt;=1,"完了",IF(I71&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:17">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="H72" s="7">
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="H72" s="8">
         <f>IF(OR(F72="",G72=""),"",WORKDAY.INTL(F72,G72-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L72" s="9"/>
-      <c r="M72" s="10">
+      <c r="L72" s="10"/>
+      <c r="M72" s="11">
         <f>IF(OR(F72="",I72=""),"",NETWORKDAYS.INTL(F72,I72-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N72" s="10">
+      <c r="N72" s="11">
         <f>IF(OR(H72="",J72=""),"",NETWORKDAYS.INTL(H72,J72-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P72" s="9"/>
-      <c r="Q72" s="10">
+      <c r="P72" s="10"/>
+      <c r="Q72" s="11">
         <f>IF(C72="","",IF(E72="マイルストーン","MILESTONE",IF(K72&gt;=1,"完了",IF(I72&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:17">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="H73" s="7">
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="H73" s="8">
         <f>IF(OR(F73="",G73=""),"",WORKDAY.INTL(F73,G73-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L73" s="9"/>
-      <c r="M73" s="10">
+      <c r="L73" s="10"/>
+      <c r="M73" s="11">
         <f>IF(OR(F73="",I73=""),"",NETWORKDAYS.INTL(F73,I73-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N73" s="10">
+      <c r="N73" s="11">
         <f>IF(OR(H73="",J73=""),"",NETWORKDAYS.INTL(H73,J73-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P73" s="9"/>
-      <c r="Q73" s="10">
+      <c r="P73" s="10"/>
+      <c r="Q73" s="11">
         <f>IF(C73="","",IF(E73="マイルストーン","MILESTONE",IF(K73&gt;=1,"完了",IF(I73&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:17">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="H74" s="7">
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="H74" s="8">
         <f>IF(OR(F74="",G74=""),"",WORKDAY.INTL(F74,G74-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L74" s="9"/>
-      <c r="M74" s="10">
+      <c r="L74" s="10"/>
+      <c r="M74" s="11">
         <f>IF(OR(F74="",I74=""),"",NETWORKDAYS.INTL(F74,I74-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N74" s="10">
+      <c r="N74" s="11">
         <f>IF(OR(H74="",J74=""),"",NETWORKDAYS.INTL(H74,J74-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P74" s="9"/>
-      <c r="Q74" s="10">
+      <c r="P74" s="10"/>
+      <c r="Q74" s="11">
         <f>IF(C74="","",IF(E74="マイルストーン","MILESTONE",IF(K74&gt;=1,"完了",IF(I74&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:17">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="H75" s="7">
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="H75" s="8">
         <f>IF(OR(F75="",G75=""),"",WORKDAY.INTL(F75,G75-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L75" s="9"/>
-      <c r="M75" s="10">
+      <c r="L75" s="10"/>
+      <c r="M75" s="11">
         <f>IF(OR(F75="",I75=""),"",NETWORKDAYS.INTL(F75,I75-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N75" s="10">
+      <c r="N75" s="11">
         <f>IF(OR(H75="",J75=""),"",NETWORKDAYS.INTL(H75,J75-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P75" s="9"/>
-      <c r="Q75" s="10">
+      <c r="P75" s="10"/>
+      <c r="Q75" s="11">
         <f>IF(C75="","",IF(E75="マイルストーン","MILESTONE",IF(K75&gt;=1,"完了",IF(I75&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:17">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="H76" s="7">
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="H76" s="8">
         <f>IF(OR(F76="",G76=""),"",WORKDAY.INTL(F76,G76-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L76" s="9"/>
-      <c r="M76" s="10">
+      <c r="L76" s="10"/>
+      <c r="M76" s="11">
         <f>IF(OR(F76="",I76=""),"",NETWORKDAYS.INTL(F76,I76-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N76" s="10">
+      <c r="N76" s="11">
         <f>IF(OR(H76="",J76=""),"",NETWORKDAYS.INTL(H76,J76-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P76" s="9"/>
-      <c r="Q76" s="10">
+      <c r="P76" s="10"/>
+      <c r="Q76" s="11">
         <f>IF(C76="","",IF(E76="マイルストーン","MILESTONE",IF(K76&gt;=1,"完了",IF(I76&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:17">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="H77" s="7">
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="H77" s="8">
         <f>IF(OR(F77="",G77=""),"",WORKDAY.INTL(F77,G77-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L77" s="9"/>
-      <c r="M77" s="10">
+      <c r="L77" s="10"/>
+      <c r="M77" s="11">
         <f>IF(OR(F77="",I77=""),"",NETWORKDAYS.INTL(F77,I77-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N77" s="10">
+      <c r="N77" s="11">
         <f>IF(OR(H77="",J77=""),"",NETWORKDAYS.INTL(H77,J77-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P77" s="9"/>
-      <c r="Q77" s="10">
+      <c r="P77" s="10"/>
+      <c r="Q77" s="11">
         <f>IF(C77="","",IF(E77="マイルストーン","MILESTONE",IF(K77&gt;=1,"完了",IF(I77&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:17">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="H78" s="7">
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="H78" s="8">
         <f>IF(OR(F78="",G78=""),"",WORKDAY.INTL(F78,G78-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L78" s="9"/>
-      <c r="M78" s="10">
+      <c r="L78" s="10"/>
+      <c r="M78" s="11">
         <f>IF(OR(F78="",I78=""),"",NETWORKDAYS.INTL(F78,I78-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N78" s="10">
+      <c r="N78" s="11">
         <f>IF(OR(H78="",J78=""),"",NETWORKDAYS.INTL(H78,J78-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P78" s="9"/>
-      <c r="Q78" s="10">
+      <c r="P78" s="10"/>
+      <c r="Q78" s="11">
         <f>IF(C78="","",IF(E78="マイルストーン","MILESTONE",IF(K78&gt;=1,"完了",IF(I78&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:17">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="H79" s="7">
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="H79" s="8">
         <f>IF(OR(F79="",G79=""),"",WORKDAY.INTL(F79,G79-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L79" s="9"/>
-      <c r="M79" s="10">
+      <c r="L79" s="10"/>
+      <c r="M79" s="11">
         <f>IF(OR(F79="",I79=""),"",NETWORKDAYS.INTL(F79,I79-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N79" s="10">
+      <c r="N79" s="11">
         <f>IF(OR(H79="",J79=""),"",NETWORKDAYS.INTL(H79,J79-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P79" s="9"/>
-      <c r="Q79" s="10">
+      <c r="P79" s="10"/>
+      <c r="Q79" s="11">
         <f>IF(C79="","",IF(E79="マイルストーン","MILESTONE",IF(K79&gt;=1,"完了",IF(I79&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:17">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="H80" s="7">
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="H80" s="8">
         <f>IF(OR(F80="",G80=""),"",WORKDAY.INTL(F80,G80-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L80" s="9"/>
-      <c r="M80" s="10">
+      <c r="L80" s="10"/>
+      <c r="M80" s="11">
         <f>IF(OR(F80="",I80=""),"",NETWORKDAYS.INTL(F80,I80-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N80" s="10">
+      <c r="N80" s="11">
         <f>IF(OR(H80="",J80=""),"",NETWORKDAYS.INTL(H80,J80-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P80" s="9"/>
-      <c r="Q80" s="10">
+      <c r="P80" s="10"/>
+      <c r="Q80" s="11">
         <f>IF(C80="","",IF(E80="マイルストーン","MILESTONE",IF(K80&gt;=1,"完了",IF(I80&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:17">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="H81" s="7">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="H81" s="8">
         <f>IF(OR(F81="",G81=""),"",WORKDAY.INTL(F81,G81-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L81" s="9"/>
-      <c r="M81" s="10">
+      <c r="L81" s="10"/>
+      <c r="M81" s="11">
         <f>IF(OR(F81="",I81=""),"",NETWORKDAYS.INTL(F81,I81-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N81" s="10">
+      <c r="N81" s="11">
         <f>IF(OR(H81="",J81=""),"",NETWORKDAYS.INTL(H81,J81-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P81" s="9"/>
-      <c r="Q81" s="10">
+      <c r="P81" s="10"/>
+      <c r="Q81" s="11">
         <f>IF(C81="","",IF(E81="マイルストーン","MILESTONE",IF(K81&gt;=1,"完了",IF(I81&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:17">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="H82" s="7">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="H82" s="8">
         <f>IF(OR(F82="",G82=""),"",WORKDAY.INTL(F82,G82-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L82" s="9"/>
-      <c r="M82" s="10">
+      <c r="L82" s="10"/>
+      <c r="M82" s="11">
         <f>IF(OR(F82="",I82=""),"",NETWORKDAYS.INTL(F82,I82-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N82" s="10">
+      <c r="N82" s="11">
         <f>IF(OR(H82="",J82=""),"",NETWORKDAYS.INTL(H82,J82-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P82" s="9"/>
-      <c r="Q82" s="10">
+      <c r="P82" s="10"/>
+      <c r="Q82" s="11">
         <f>IF(C82="","",IF(E82="マイルストーン","MILESTONE",IF(K82&gt;=1,"完了",IF(I82&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:17">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="H83" s="7">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="H83" s="8">
         <f>IF(OR(F83="",G83=""),"",WORKDAY.INTL(F83,G83-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L83" s="9"/>
-      <c r="M83" s="10">
+      <c r="L83" s="10"/>
+      <c r="M83" s="11">
         <f>IF(OR(F83="",I83=""),"",NETWORKDAYS.INTL(F83,I83-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N83" s="10">
+      <c r="N83" s="11">
         <f>IF(OR(H83="",J83=""),"",NETWORKDAYS.INTL(H83,J83-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P83" s="9"/>
-      <c r="Q83" s="10">
+      <c r="P83" s="10"/>
+      <c r="Q83" s="11">
         <f>IF(C83="","",IF(E83="マイルストーン","MILESTONE",IF(K83&gt;=1,"完了",IF(I83&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:17">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="H84" s="7">
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
+      <c r="H84" s="8">
         <f>IF(OR(F84="",G84=""),"",WORKDAY.INTL(F84,G84-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L84" s="9"/>
-      <c r="M84" s="10">
+      <c r="L84" s="10"/>
+      <c r="M84" s="11">
         <f>IF(OR(F84="",I84=""),"",NETWORKDAYS.INTL(F84,I84-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N84" s="10">
+      <c r="N84" s="11">
         <f>IF(OR(H84="",J84=""),"",NETWORKDAYS.INTL(H84,J84-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P84" s="9"/>
-      <c r="Q84" s="10">
+      <c r="P84" s="10"/>
+      <c r="Q84" s="11">
         <f>IF(C84="","",IF(E84="マイルストーン","MILESTONE",IF(K84&gt;=1,"完了",IF(I84&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:17">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="H85" s="7">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="H85" s="8">
         <f>IF(OR(F85="",G85=""),"",WORKDAY.INTL(F85,G85-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L85" s="9"/>
-      <c r="M85" s="10">
+      <c r="L85" s="10"/>
+      <c r="M85" s="11">
         <f>IF(OR(F85="",I85=""),"",NETWORKDAYS.INTL(F85,I85-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N85" s="10">
+      <c r="N85" s="11">
         <f>IF(OR(H85="",J85=""),"",NETWORKDAYS.INTL(H85,J85-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P85" s="9"/>
-      <c r="Q85" s="10">
+      <c r="P85" s="10"/>
+      <c r="Q85" s="11">
         <f>IF(C85="","",IF(E85="マイルストーン","MILESTONE",IF(K85&gt;=1,"完了",IF(I85&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:17">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="H86" s="7">
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="H86" s="8">
         <f>IF(OR(F86="",G86=""),"",WORKDAY.INTL(F86,G86-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L86" s="9"/>
-      <c r="M86" s="10">
+      <c r="L86" s="10"/>
+      <c r="M86" s="11">
         <f>IF(OR(F86="",I86=""),"",NETWORKDAYS.INTL(F86,I86-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N86" s="10">
+      <c r="N86" s="11">
         <f>IF(OR(H86="",J86=""),"",NETWORKDAYS.INTL(H86,J86-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P86" s="9"/>
-      <c r="Q86" s="10">
+      <c r="P86" s="10"/>
+      <c r="Q86" s="11">
         <f>IF(C86="","",IF(E86="マイルストーン","MILESTONE",IF(K86&gt;=1,"完了",IF(I86&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:17">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="H87" s="7">
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="H87" s="8">
         <f>IF(OR(F87="",G87=""),"",WORKDAY.INTL(F87,G87-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L87" s="9"/>
-      <c r="M87" s="10">
+      <c r="L87" s="10"/>
+      <c r="M87" s="11">
         <f>IF(OR(F87="",I87=""),"",NETWORKDAYS.INTL(F87,I87-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N87" s="10">
+      <c r="N87" s="11">
         <f>IF(OR(H87="",J87=""),"",NETWORKDAYS.INTL(H87,J87-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P87" s="9"/>
-      <c r="Q87" s="10">
+      <c r="P87" s="10"/>
+      <c r="Q87" s="11">
         <f>IF(C87="","",IF(E87="マイルストーン","MILESTONE",IF(K87&gt;=1,"完了",IF(I87&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:17">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="H88" s="7">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="H88" s="8">
         <f>IF(OR(F88="",G88=""),"",WORKDAY.INTL(F88,G88-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L88" s="9"/>
-      <c r="M88" s="10">
+      <c r="L88" s="10"/>
+      <c r="M88" s="11">
         <f>IF(OR(F88="",I88=""),"",NETWORKDAYS.INTL(F88,I88-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N88" s="10">
+      <c r="N88" s="11">
         <f>IF(OR(H88="",J88=""),"",NETWORKDAYS.INTL(H88,J88-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P88" s="9"/>
-      <c r="Q88" s="10">
+      <c r="P88" s="10"/>
+      <c r="Q88" s="11">
         <f>IF(C88="","",IF(E88="マイルストーン","MILESTONE",IF(K88&gt;=1,"完了",IF(I88&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:17">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="H89" s="7">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="H89" s="8">
         <f>IF(OR(F89="",G89=""),"",WORKDAY.INTL(F89,G89-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L89" s="9"/>
-      <c r="M89" s="10">
+      <c r="L89" s="10"/>
+      <c r="M89" s="11">
         <f>IF(OR(F89="",I89=""),"",NETWORKDAYS.INTL(F89,I89-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N89" s="10">
+      <c r="N89" s="11">
         <f>IF(OR(H89="",J89=""),"",NETWORKDAYS.INTL(H89,J89-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P89" s="9"/>
-      <c r="Q89" s="10">
+      <c r="P89" s="10"/>
+      <c r="Q89" s="11">
         <f>IF(C89="","",IF(E89="マイルストーン","MILESTONE",IF(K89&gt;=1,"完了",IF(I89&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:17">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="H90" s="7">
+      <c r="A90" s="10"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="H90" s="8">
         <f>IF(OR(F90="",G90=""),"",WORKDAY.INTL(F90,G90-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L90" s="9"/>
-      <c r="M90" s="10">
+      <c r="L90" s="10"/>
+      <c r="M90" s="11">
         <f>IF(OR(F90="",I90=""),"",NETWORKDAYS.INTL(F90,I90-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N90" s="10">
+      <c r="N90" s="11">
         <f>IF(OR(H90="",J90=""),"",NETWORKDAYS.INTL(H90,J90-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P90" s="9"/>
-      <c r="Q90" s="10">
+      <c r="P90" s="10"/>
+      <c r="Q90" s="11">
         <f>IF(C90="","",IF(E90="マイルストーン","MILESTONE",IF(K90&gt;=1,"完了",IF(I90&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:17">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="H91" s="7">
+      <c r="A91" s="10"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="H91" s="8">
         <f>IF(OR(F91="",G91=""),"",WORKDAY.INTL(F91,G91-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L91" s="9"/>
-      <c r="M91" s="10">
+      <c r="L91" s="10"/>
+      <c r="M91" s="11">
         <f>IF(OR(F91="",I91=""),"",NETWORKDAYS.INTL(F91,I91-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N91" s="10">
+      <c r="N91" s="11">
         <f>IF(OR(H91="",J91=""),"",NETWORKDAYS.INTL(H91,J91-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P91" s="9"/>
-      <c r="Q91" s="10">
+      <c r="P91" s="10"/>
+      <c r="Q91" s="11">
         <f>IF(C91="","",IF(E91="マイルストーン","MILESTONE",IF(K91&gt;=1,"完了",IF(I91&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:17">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="H92" s="7">
+      <c r="A92" s="10"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="H92" s="8">
         <f>IF(OR(F92="",G92=""),"",WORKDAY.INTL(F92,G92-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L92" s="9"/>
-      <c r="M92" s="10">
+      <c r="L92" s="10"/>
+      <c r="M92" s="11">
         <f>IF(OR(F92="",I92=""),"",NETWORKDAYS.INTL(F92,I92-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N92" s="10">
+      <c r="N92" s="11">
         <f>IF(OR(H92="",J92=""),"",NETWORKDAYS.INTL(H92,J92-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P92" s="9"/>
-      <c r="Q92" s="10">
+      <c r="P92" s="10"/>
+      <c r="Q92" s="11">
         <f>IF(C92="","",IF(E92="マイルストーン","MILESTONE",IF(K92&gt;=1,"完了",IF(I92&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="H93" s="7">
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="H93" s="8">
         <f>IF(OR(F93="",G93=""),"",WORKDAY.INTL(F93,G93-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L93" s="9"/>
-      <c r="M93" s="10">
+      <c r="L93" s="10"/>
+      <c r="M93" s="11">
         <f>IF(OR(F93="",I93=""),"",NETWORKDAYS.INTL(F93,I93-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N93" s="10">
+      <c r="N93" s="11">
         <f>IF(OR(H93="",J93=""),"",NETWORKDAYS.INTL(H93,J93-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P93" s="9"/>
-      <c r="Q93" s="10">
+      <c r="P93" s="10"/>
+      <c r="Q93" s="11">
         <f>IF(C93="","",IF(E93="マイルストーン","MILESTONE",IF(K93&gt;=1,"完了",IF(I93&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:17">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="H94" s="7">
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="H94" s="8">
         <f>IF(OR(F94="",G94=""),"",WORKDAY.INTL(F94,G94-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L94" s="9"/>
-      <c r="M94" s="10">
+      <c r="L94" s="10"/>
+      <c r="M94" s="11">
         <f>IF(OR(F94="",I94=""),"",NETWORKDAYS.INTL(F94,I94-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N94" s="10">
+      <c r="N94" s="11">
         <f>IF(OR(H94="",J94=""),"",NETWORKDAYS.INTL(H94,J94-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P94" s="9"/>
-      <c r="Q94" s="10">
+      <c r="P94" s="10"/>
+      <c r="Q94" s="11">
         <f>IF(C94="","",IF(E94="マイルストーン","MILESTONE",IF(K94&gt;=1,"完了",IF(I94&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:17">
-      <c r="A95" s="9"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="H95" s="7">
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10"/>
+      <c r="H95" s="8">
         <f>IF(OR(F95="",G95=""),"",WORKDAY.INTL(F95,G95-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L95" s="9"/>
-      <c r="M95" s="10">
+      <c r="L95" s="10"/>
+      <c r="M95" s="11">
         <f>IF(OR(F95="",I95=""),"",NETWORKDAYS.INTL(F95,I95-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N95" s="10">
+      <c r="N95" s="11">
         <f>IF(OR(H95="",J95=""),"",NETWORKDAYS.INTL(H95,J95-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P95" s="9"/>
-      <c r="Q95" s="10">
+      <c r="P95" s="10"/>
+      <c r="Q95" s="11">
         <f>IF(C95="","",IF(E95="マイルストーン","MILESTONE",IF(K95&gt;=1,"完了",IF(I95&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:17">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="H96" s="7">
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="H96" s="8">
         <f>IF(OR(F96="",G96=""),"",WORKDAY.INTL(F96,G96-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L96" s="9"/>
-      <c r="M96" s="10">
+      <c r="L96" s="10"/>
+      <c r="M96" s="11">
         <f>IF(OR(F96="",I96=""),"",NETWORKDAYS.INTL(F96,I96-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N96" s="10">
+      <c r="N96" s="11">
         <f>IF(OR(H96="",J96=""),"",NETWORKDAYS.INTL(H96,J96-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P96" s="9"/>
-      <c r="Q96" s="10">
+      <c r="P96" s="10"/>
+      <c r="Q96" s="11">
         <f>IF(C96="","",IF(E96="マイルストーン","MILESTONE",IF(K96&gt;=1,"完了",IF(I96&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:17">
-      <c r="A97" s="9"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="H97" s="7">
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="H97" s="8">
         <f>IF(OR(F97="",G97=""),"",WORKDAY.INTL(F97,G97-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L97" s="9"/>
-      <c r="M97" s="10">
+      <c r="L97" s="10"/>
+      <c r="M97" s="11">
         <f>IF(OR(F97="",I97=""),"",NETWORKDAYS.INTL(F97,I97-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N97" s="10">
+      <c r="N97" s="11">
         <f>IF(OR(H97="",J97=""),"",NETWORKDAYS.INTL(H97,J97-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P97" s="9"/>
-      <c r="Q97" s="10">
+      <c r="P97" s="10"/>
+      <c r="Q97" s="11">
         <f>IF(C97="","",IF(E97="マイルストーン","MILESTONE",IF(K97&gt;=1,"完了",IF(I97&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:17">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="H98" s="7">
+      <c r="A98" s="10"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="H98" s="8">
         <f>IF(OR(F98="",G98=""),"",WORKDAY.INTL(F98,G98-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L98" s="9"/>
-      <c r="M98" s="10">
+      <c r="L98" s="10"/>
+      <c r="M98" s="11">
         <f>IF(OR(F98="",I98=""),"",NETWORKDAYS.INTL(F98,I98-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N98" s="10">
+      <c r="N98" s="11">
         <f>IF(OR(H98="",J98=""),"",NETWORKDAYS.INTL(H98,J98-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P98" s="9"/>
-      <c r="Q98" s="10">
+      <c r="P98" s="10"/>
+      <c r="Q98" s="11">
         <f>IF(C98="","",IF(E98="マイルストーン","MILESTONE",IF(K98&gt;=1,"完了",IF(I98&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:17">
-      <c r="A99" s="9"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="H99" s="7">
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="H99" s="8">
         <f>IF(OR(F99="",G99=""),"",WORKDAY.INTL(F99,G99-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L99" s="9"/>
-      <c r="M99" s="10">
+      <c r="L99" s="10"/>
+      <c r="M99" s="11">
         <f>IF(OR(F99="",I99=""),"",NETWORKDAYS.INTL(F99,I99-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N99" s="10">
+      <c r="N99" s="11">
         <f>IF(OR(H99="",J99=""),"",NETWORKDAYS.INTL(H99,J99-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P99" s="9"/>
-      <c r="Q99" s="10">
+      <c r="P99" s="10"/>
+      <c r="Q99" s="11">
         <f>IF(C99="","",IF(E99="マイルストーン","MILESTONE",IF(K99&gt;=1,"完了",IF(I99&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:17">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="H100" s="7">
+      <c r="A100" s="10"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="H100" s="8">
         <f>IF(OR(F100="",G100=""),"",WORKDAY.INTL(F100,G100-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L100" s="9"/>
-      <c r="M100" s="10">
+      <c r="L100" s="10"/>
+      <c r="M100" s="11">
         <f>IF(OR(F100="",I100=""),"",NETWORKDAYS.INTL(F100,I100-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N100" s="10">
+      <c r="N100" s="11">
         <f>IF(OR(H100="",J100=""),"",NETWORKDAYS.INTL(H100,J100-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P100" s="9"/>
-      <c r="Q100" s="10">
+      <c r="P100" s="10"/>
+      <c r="Q100" s="11">
         <f>IF(C100="","",IF(E100="マイルストーン","MILESTONE",IF(K100&gt;=1,"完了",IF(I100&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:17">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="H101" s="7">
+      <c r="A101" s="10"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="H101" s="8">
         <f>IF(OR(F101="",G101=""),"",WORKDAY.INTL(F101,G101-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L101" s="9"/>
-      <c r="M101" s="10">
+      <c r="L101" s="10"/>
+      <c r="M101" s="11">
         <f>IF(OR(F101="",I101=""),"",NETWORKDAYS.INTL(F101,I101-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N101" s="10">
+      <c r="N101" s="11">
         <f>IF(OR(H101="",J101=""),"",NETWORKDAYS.INTL(H101,J101-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P101" s="9"/>
-      <c r="Q101" s="10">
+      <c r="P101" s="10"/>
+      <c r="Q101" s="11">
         <f>IF(C101="","",IF(E101="マイルストーン","MILESTONE",IF(K101&gt;=1,"完了",IF(I101&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:17">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="H102" s="7">
+      <c r="A102" s="10"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="H102" s="8">
         <f>IF(OR(F102="",G102=""),"",WORKDAY.INTL(F102,G102-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L102" s="9"/>
-      <c r="M102" s="10">
+      <c r="L102" s="10"/>
+      <c r="M102" s="11">
         <f>IF(OR(F102="",I102=""),"",NETWORKDAYS.INTL(F102,I102-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="10">
+      <c r="N102" s="11">
         <f>IF(OR(H102="",J102=""),"",NETWORKDAYS.INTL(H102,J102-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="9"/>
-      <c r="Q102" s="10">
+      <c r="P102" s="10"/>
+      <c r="Q102" s="11">
         <f>IF(C102="","",IF(E102="マイルストーン","MILESTONE",IF(K102&gt;=1,"完了",IF(I102&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:17">
-      <c r="A103" s="9"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="H103" s="7">
+      <c r="A103" s="10"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="H103" s="8">
         <f>IF(OR(F103="",G103=""),"",WORKDAY.INTL(F103,G103-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L103" s="9"/>
-      <c r="M103" s="10">
+      <c r="L103" s="10"/>
+      <c r="M103" s="11">
         <f>IF(OR(F103="",I103=""),"",NETWORKDAYS.INTL(F103,I103-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="10">
+      <c r="N103" s="11">
         <f>IF(OR(H103="",J103=""),"",NETWORKDAYS.INTL(H103,J103-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="9"/>
-      <c r="Q103" s="10">
+      <c r="P103" s="10"/>
+      <c r="Q103" s="11">
         <f>IF(C103="","",IF(E103="マイルストーン","MILESTONE",IF(K103&gt;=1,"完了",IF(I103&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:17">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="H104" s="7">
+      <c r="A104" s="10"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="H104" s="8">
         <f>IF(OR(F104="",G104=""),"",WORKDAY.INTL(F104,G104-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L104" s="9"/>
-      <c r="M104" s="10">
+      <c r="L104" s="10"/>
+      <c r="M104" s="11">
         <f>IF(OR(F104="",I104=""),"",NETWORKDAYS.INTL(F104,I104-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N104" s="10">
+      <c r="N104" s="11">
         <f>IF(OR(H104="",J104=""),"",NETWORKDAYS.INTL(H104,J104-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P104" s="9"/>
-      <c r="Q104" s="10">
+      <c r="P104" s="10"/>
+      <c r="Q104" s="11">
         <f>IF(C104="","",IF(E104="マイルストーン","MILESTONE",IF(K104&gt;=1,"完了",IF(I104&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:17">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
-      <c r="H105" s="7">
+      <c r="A105" s="10"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="10"/>
+      <c r="D105" s="10"/>
+      <c r="E105" s="10"/>
+      <c r="H105" s="8">
         <f>IF(OR(F105="",G105=""),"",WORKDAY.INTL(F105,G105-1,1,休日!$A$4:$A$200))</f>
         <v>0</v>
       </c>
-      <c r="L105" s="9"/>
-      <c r="M105" s="10">
+      <c r="L105" s="10"/>
+      <c r="M105" s="11">
         <f>IF(OR(F105="",I105=""),"",NETWORKDAYS.INTL(F105,I105-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="N105" s="10">
+      <c r="N105" s="11">
         <f>IF(OR(H105="",J105=""),"",NETWORKDAYS.INTL(H105,J105-1,1,休日!$A$4:$A$200)-1)</f>
         <v>0</v>
       </c>
-      <c r="P105" s="9"/>
-      <c r="Q105" s="10">
+      <c r="P105" s="10"/>
+      <c r="Q105" s="11">
         <f>IF(C105="","",IF(E105="マイルストーン","MILESTONE",IF(K105&gt;=1,"完了",IF(I105&lt;&gt;"","進行中","未着手"))))</f>
         <v>0</v>
       </c>
@@ -4318,7 +5809,7 @@
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="R6:EG105">
+  <conditionalFormatting sqref="R6:NS105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(R$5&gt;=$F6,R$5&lt;=$H6,$C6&lt;&gt;"")</formula>
     </cfRule>
@@ -4348,7 +5839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -4357,61 +5848,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
+        <v>46296</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15">
+        <v>46447</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <f>TODAY()</f>
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="13">
-        <v>46296</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B8" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>120</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13">
-        <f>TODAY()</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4429,40 +5931,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="12" t="s">
-        <v>12</v>
+      <c r="A1" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>14</v>
+      <c r="A3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>46307</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>15</v>
+      <c r="B4" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="15">
+      <c r="A5" s="17">
         <v>46329</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>16</v>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>46349</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>17</v>
+      <c r="B6" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4483,86 +5985,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="12" t="s">
-        <v>62</v>
+      <c r="A1" s="13" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="18">
         <f>COUNTIF(WBS!$C$6:$C$105,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="16">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="18">
         <f>COUNTIF(WBS!$Q$6:$Q$105,"完了")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="18">
         <f>COUNTIF(WBS!$Q$6:$Q$105,"進行中")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="17">
+      <c r="A6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="19">
         <f>IFERROR(AVERAGE(WBS!$K$6:$K$105),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="16">
+      <c r="A7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="18">
         <f>COUNTIF(WBS!$N$6:$N$105,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="16">
+      <c r="A8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="18">
         <f>SUM(WBS!$O$6:$O$105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
-        <v>69</v>
+      <c r="A11" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="B12" s="20"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="19"/>
+        <v>74</v>
+      </c>
+      <c r="B13" s="21"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="20"/>
+        <v>75</v>
+      </c>
+      <c r="B14" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WBS/開発マイルストーン_WBS.xlsx
+++ b/WBS/開発マイルストーン_WBS.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="77">
   <si>
     <t>開発マイルストーン WBS</t>
   </si>
@@ -61,7 +61,10 @@
     <t>VBAの AddWBSRow で入力行を追加できます。</t>
   </si>
   <si>
-    <t>VBAの InputWBSRow で選択行へ入力ダイアログを表示できます。</t>
+    <t>VBAの InputWBSRow で種類別フォームが開き、当該行を補助します。</t>
+  </si>
+  <si>
+    <t>フェーズ / タスク / マイルストーンの入力フォームで、各行の情報を段階的に入力できます。</t>
   </si>
   <si>
     <t>休日シートに日付を追加すると、予定終了日から除外されます。</t>
@@ -411,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -442,7 +445,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -840,7 +849,7 @@
     </row>
     <row r="2" spans="1:383">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1961,55 +1970,55 @@
     </row>
     <row r="5" spans="1:383" ht="34" customHeight="1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R5" s="4">
         <v>46296</v>
@@ -3112,19 +3121,19 @@
     </row>
     <row r="6" spans="1:383">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="6">
         <v>46296</v>
@@ -3152,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q6" s="11">
         <f>IF(C6="","",IF(E6="マイルストーン","MILESTONE",IF(K6&gt;=1,"完了",IF(I6&lt;&gt;"","進行中","未着手"))))</f>
@@ -3161,19 +3170,19 @@
     </row>
     <row r="7" spans="1:383">
       <c r="A7" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="10">
         <v>1</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>45</v>
+      <c r="C7" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="6">
         <v>46296</v>
@@ -3208,19 +3217,19 @@
     </row>
     <row r="8" spans="1:383">
       <c r="A8" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="10">
         <v>1</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>48</v>
+      <c r="C8" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="6">
         <v>46297</v>
@@ -3236,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M8" s="11">
         <f>IF(OR(F8="",I8=""),"",NETWORKDAYS.INTL(F8,I8-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3256,20 +3265,20 @@
       </c>
     </row>
     <row r="9" spans="1:383">
-      <c r="A9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="13">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="12" t="s">
+      <c r="C9" s="14" t="s">
         <v>52</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="F9" s="6">
         <v>46303</v>
@@ -3285,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" s="11">
         <f>IF(OR(F9="",I9=""),"",NETWORKDAYS.INTL(F9,I9-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3299,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="11">
         <f>IF(C9="","",IF(E9="マイルストーン","MILESTONE",IF(K9&gt;=1,"完了",IF(I9&lt;&gt;"","進行中","未着手"))))</f>
@@ -3308,19 +3317,19 @@
     </row>
     <row r="10" spans="1:383">
       <c r="A10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F10" s="6">
         <v>46306</v>
@@ -3336,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" s="11">
         <f>IF(OR(F10="",I10=""),"",NETWORKDAYS.INTL(F10,I10-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3357,19 +3366,19 @@
     </row>
     <row r="11" spans="1:383">
       <c r="A11" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="10">
         <v>1</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>57</v>
+      <c r="C11" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" s="6">
         <v>46306</v>
@@ -3385,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M11" s="11">
         <f>IF(OR(F11="",I11=""),"",NETWORKDAYS.INTL(F11,I11-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3406,19 +3415,19 @@
     </row>
     <row r="12" spans="1:383">
       <c r="A12" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="10">
         <v>1</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>60</v>
+      <c r="C12" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="6">
         <v>46314</v>
@@ -3434,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M12" s="11">
         <f>IF(OR(F12="",I12=""),"",NETWORKDAYS.INTL(F12,I12-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3454,20 +3463,20 @@
       </c>
     </row>
     <row r="13" spans="1:383">
-      <c r="A13" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="A13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="13">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>52</v>
+      <c r="C13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="F13" s="6">
         <v>46335</v>
@@ -3483,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M13" s="11">
         <f>IF(OR(F13="",I13=""),"",NETWORKDAYS.INTL(F13,I13-1,1,休日!$A$4:$A$200)-1)</f>
@@ -3497,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="11">
         <f>IF(C13="","",IF(E13="マイルストーン","MILESTONE",IF(K13&gt;=1,"完了",IF(I13&lt;&gt;"","進行中","未着手"))))</f>
@@ -5848,7 +5857,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5867,7 +5876,7 @@
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="16">
         <v>46296</v>
       </c>
       <c r="D4" t="s">
@@ -5878,7 +5887,7 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>46447</v>
       </c>
       <c r="D5" t="s">
@@ -5900,7 +5909,7 @@
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="16">
         <f>TODAY()</f>
         <v>0</v>
       </c>
@@ -5914,6 +5923,9 @@
       </c>
       <c r="B8" t="s">
         <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5931,40 +5943,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="13" t="s">
-        <v>15</v>
+      <c r="A1" s="15" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>17</v>
       </c>
+      <c r="B3" s="18" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="17">
+      <c r="A4" s="19">
         <v>46307</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="17">
+      <c r="A5" s="19">
         <v>46329</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="17">
+      <c r="A6" s="19">
         <v>46349</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -5985,86 +5997,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="13" t="s">
-        <v>65</v>
+      <c r="A1" s="15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="18">
+        <v>67</v>
+      </c>
+      <c r="B3" s="20">
         <f>COUNTIF(WBS!$C$6:$C$105,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="18">
+        <v>68</v>
+      </c>
+      <c r="B4" s="20">
         <f>COUNTIF(WBS!$Q$6:$Q$105,"完了")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="18">
+        <v>69</v>
+      </c>
+      <c r="B5" s="20">
         <f>COUNTIF(WBS!$Q$6:$Q$105,"進行中")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="19">
+        <v>70</v>
+      </c>
+      <c r="B6" s="21">
         <f>IFERROR(AVERAGE(WBS!$K$6:$K$105),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="18">
+        <v>71</v>
+      </c>
+      <c r="B7" s="20">
         <f>COUNTIF(WBS!$N$6:$N$105,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="18">
+        <v>72</v>
+      </c>
+      <c r="B8" s="20">
         <f>SUM(WBS!$O$6:$O$105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="21"/>
+        <v>75</v>
+      </c>
+      <c r="B13" s="23"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="22"/>
+        <v>76</v>
+      </c>
+      <c r="B14" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
